--- a/excel/solarvy_final_version.xlsx
+++ b/excel/solarvy_final_version.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d0bdc482b6854592/Documents/Solarvy/Ratheesh/Working copy/solarvy v1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="210" documentId="8_{92B6309A-027A-495D-83F1-D4B686E86F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A976403-49BF-4A5B-AE59-AED808A08788}"/>
+  <xr:revisionPtr revIDLastSave="347" documentId="8_{92B6309A-027A-495D-83F1-D4B686E86F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F682646-F897-451B-9259-9AE89BB8B2D1}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="823" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="823" firstSheet="25" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,15 @@
     <sheet name="Introduction_Tracker" sheetId="24" r:id="rId25"/>
     <sheet name="Quote_Review_Tracker" sheetId="25" r:id="rId26"/>
     <sheet name="PDF Inputs" sheetId="27" r:id="rId27"/>
+    <sheet name="Finance_Request" sheetId="28" r:id="rId28"/>
+    <sheet name="Finance_Partners" sheetId="29" r:id="rId29"/>
+    <sheet name="Finance_Products" sheetId="30" r:id="rId30"/>
+    <sheet name="Finance_Matches" sheetId="31" r:id="rId31"/>
+    <sheet name="Partner_Choice" sheetId="32" r:id="rId32"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId33"/>
+  </externalReferences>
   <definedNames>
     <definedName name="Commercial">User_Inputs!$L$20:$L$28</definedName>
     <definedName name="Factory">User_Inputs!$L$31:$L$38</definedName>
@@ -160,7 +168,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2983" uniqueCount="1031">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3234" uniqueCount="1170">
   <si>
     <t>Solarvy Energy Platform Calculation Engine - Master Workbook</t>
   </si>
@@ -3296,7 +3304,424 @@
     <t>0-2 hours, 3-6 hours, 7-12 hours, 13-18 hours, 19-24 hours</t>
   </si>
   <si>
-    <t>7-12 hours</t>
+    <t>2-6 hours</t>
+  </si>
+  <si>
+    <t>Project cost (NGN)</t>
+  </si>
+  <si>
+    <t>Applicant type</t>
+  </si>
+  <si>
+    <t>Individual / Homeowner</t>
+  </si>
+  <si>
+    <t>Deposit available (NGN)</t>
+  </si>
+  <si>
+    <t>Amount requested (NGN)</t>
+  </si>
+  <si>
+    <t>Preferred finance route</t>
+  </si>
+  <si>
+    <t>Solarvy Finance Request</t>
+  </si>
+  <si>
+    <t>PV size (kWp)</t>
+  </si>
+  <si>
+    <t>Battery size (kWh)</t>
+  </si>
+  <si>
+    <t>Annual net energy savings (NGN)</t>
+  </si>
+  <si>
+    <t>Deposit percentage</t>
+  </si>
+  <si>
+    <t>Asset financing</t>
+  </si>
+  <si>
+    <t>Repayment term (months)</t>
+  </si>
+  <si>
+    <t>Monthly income (NGN)</t>
+  </si>
+  <si>
+    <t>Consent to share enquiry</t>
+  </si>
+  <si>
+    <t>Finance request valid</t>
+  </si>
+  <si>
+    <t>Amount you want to Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes </t>
+  </si>
+  <si>
+    <t>Choose type of financing - under the Potential financing routes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculated deposit </t>
+  </si>
+  <si>
+    <t>Partner ID</t>
+  </si>
+  <si>
+    <t>FICTIONAL lender / provider</t>
+  </si>
+  <si>
+    <t>Provider type</t>
+  </si>
+  <si>
+    <t>Verification</t>
+  </si>
+  <si>
+    <t>Operating states</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Finance company</t>
+  </si>
+  <si>
+    <t>Lagos, Oyo, Ebonyi</t>
+  </si>
+  <si>
+    <t>Not applicable</t>
+  </si>
+  <si>
+    <t>Lagos, Akwa Ibom, FCT</t>
+  </si>
+  <si>
+    <t>Energy service provider</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>Lagos, Ogun, Rivers</t>
+  </si>
+  <si>
+    <t>Instalment provider</t>
+  </si>
+  <si>
+    <t>SME lender</t>
+  </si>
+  <si>
+    <t>Lagos, Abuja, Rivers</t>
+  </si>
+  <si>
+    <t>Lagos, Oyo, FCT</t>
+  </si>
+  <si>
+    <t>Lagos, Akwa Ibom</t>
+  </si>
+  <si>
+    <t>P001</t>
+  </si>
+  <si>
+    <t>P002</t>
+  </si>
+  <si>
+    <t>P003</t>
+  </si>
+  <si>
+    <t>P004</t>
+  </si>
+  <si>
+    <t>P005</t>
+  </si>
+  <si>
+    <t>P006</t>
+  </si>
+  <si>
+    <t>P007</t>
+  </si>
+  <si>
+    <t>P008</t>
+  </si>
+  <si>
+    <t>P009</t>
+  </si>
+  <si>
+    <t>P010</t>
+  </si>
+  <si>
+    <t>P011</t>
+  </si>
+  <si>
+    <t>P012</t>
+  </si>
+  <si>
+    <t>SunBridge Capital</t>
+  </si>
+  <si>
+    <t>Helio Credit</t>
+  </si>
+  <si>
+    <t>BrightLease Energy</t>
+  </si>
+  <si>
+    <t>GreenGrid Funding</t>
+  </si>
+  <si>
+    <t>HomeSolar Finance</t>
+  </si>
+  <si>
+    <t>SME Power Credit</t>
+  </si>
+  <si>
+    <t>Community Solar Plans</t>
+  </si>
+  <si>
+    <t>Horizon Energy Services</t>
+  </si>
+  <si>
+    <t>SolarFlex Capital</t>
+  </si>
+  <si>
+    <t>PowerPath Funding</t>
+  </si>
+  <si>
+    <t>SunNest Instalments</t>
+  </si>
+  <si>
+    <t>Commercial Energy Lease</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NOT VERIFIED</t>
+  </si>
+  <si>
+    <t>NOT VERIFIED</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> No licence, contact or offer</t>
+  </si>
+  <si>
+    <t>Product ID</t>
+  </si>
+  <si>
+    <t>Product name</t>
+  </si>
+  <si>
+    <t>Finance route</t>
+  </si>
+  <si>
+    <t>States served</t>
+  </si>
+  <si>
+    <t>Min loan NGN</t>
+  </si>
+  <si>
+    <t>Max loan NGN</t>
+  </si>
+  <si>
+    <t>Min deposit %</t>
+  </si>
+  <si>
+    <t>Min term months</t>
+  </si>
+  <si>
+    <t>Max term months</t>
+  </si>
+  <si>
+    <t>Nominal annual rate</t>
+  </si>
+  <si>
+    <t>Upfront fee NGN</t>
+  </si>
+  <si>
+    <t>Monthly fee NGN</t>
+  </si>
+  <si>
+    <t>Conditions / documents</t>
+  </si>
+  <si>
+    <t>Product status</t>
+  </si>
+  <si>
+    <t>SunBridge Asset Loan</t>
+  </si>
+  <si>
+    <t>Helio Asset Loan</t>
+  </si>
+  <si>
+    <t>BrightLease Energy Service</t>
+  </si>
+  <si>
+    <t>Energy-as-a-Service / lease</t>
+  </si>
+  <si>
+    <t>GreenGrid Asset Loan</t>
+  </si>
+  <si>
+    <t>HomeSolar Instalment</t>
+  </si>
+  <si>
+    <t>Solar instalment plan</t>
+  </si>
+  <si>
+    <t>SME Asset Loan</t>
+  </si>
+  <si>
+    <t>Community Instalment</t>
+  </si>
+  <si>
+    <t>Horizon Energy Service</t>
+  </si>
+  <si>
+    <t>SolarFlex Asset Loan</t>
+  </si>
+  <si>
+    <t>PowerPath Asset Loan</t>
+  </si>
+  <si>
+    <t>SunNest Instalment</t>
+  </si>
+  <si>
+    <t>Commercial Energy Service</t>
+  </si>
+  <si>
+    <t>ID, proof of address, income evidence, credit review and signed agreement.</t>
+  </si>
+  <si>
+    <t>ID, proof of address, income evidence, credit review and signed agreement</t>
+  </si>
+  <si>
+    <t>ID, address, income evidence; lender credit assessment. EaaS requires a separate usage-based quote</t>
+  </si>
+  <si>
+    <t>ID, address, income evidence, lender credit assessment, EaaS requires a separate usage-based quote</t>
+  </si>
+  <si>
+    <t>Provider</t>
+  </si>
+  <si>
+    <t>Financing type</t>
+  </si>
+  <si>
+    <t>Amount OK</t>
+  </si>
+  <si>
+    <t>Deposit OK</t>
+  </si>
+  <si>
+    <t>Term OK</t>
+  </si>
+  <si>
+    <t>Applicant OK</t>
+  </si>
+  <si>
+    <t>State OK</t>
+  </si>
+  <si>
+    <t>Route OK</t>
+  </si>
+  <si>
+    <t>MATCH RESULT</t>
+  </si>
+  <si>
+    <t>Monthly repayment NGN</t>
+  </si>
+  <si>
+    <t>Total repayment NGN</t>
+  </si>
+  <si>
+    <t>Conditions</t>
+  </si>
+  <si>
+    <t>F001</t>
+  </si>
+  <si>
+    <t>F002</t>
+  </si>
+  <si>
+    <t>F003</t>
+  </si>
+  <si>
+    <t>F004</t>
+  </si>
+  <si>
+    <t>F005</t>
+  </si>
+  <si>
+    <t>F006</t>
+  </si>
+  <si>
+    <t>F007</t>
+  </si>
+  <si>
+    <t>F008</t>
+  </si>
+  <si>
+    <t>F009</t>
+  </si>
+  <si>
+    <t>F010</t>
+  </si>
+  <si>
+    <t>F011</t>
+  </si>
+  <si>
+    <t>F012</t>
+  </si>
+  <si>
+    <t>24-36 months</t>
+  </si>
+  <si>
+    <t>SELECTED FINANCING PRODUCT</t>
+  </si>
+  <si>
+    <t>Selected Product ID</t>
+  </si>
+  <si>
+    <t>Partner name</t>
+  </si>
+  <si>
+    <t>Financing route</t>
+  </si>
+  <si>
+    <t>Preliminary matching result</t>
+  </si>
+  <si>
+    <t>Financing requested (NGN)</t>
+  </si>
+  <si>
+    <t>Deposit (NGN)</t>
+  </si>
+  <si>
+    <t>Term (months)</t>
+  </si>
+  <si>
+    <t>Nominal annual interest</t>
+  </si>
+  <si>
+    <t>Monthly repayment (NGN)</t>
+  </si>
+  <si>
+    <t>Upfront fee (NGN)</t>
+  </si>
+  <si>
+    <t>Total finance payments (NGN)</t>
+  </si>
+  <si>
+    <t>Finance conditions</t>
+  </si>
+  <si>
+    <t>Customer consent</t>
+  </si>
+  <si>
+    <t>Product ID or product selected from Finance_Matches</t>
+  </si>
+  <si>
+    <t>DETAIL</t>
+  </si>
+  <si>
+    <t>500k-1m</t>
   </si>
 </sst>
 </file>
@@ -3312,7 +3737,7 @@
     <numFmt numFmtId="169" formatCode="0.0\x"/>
     <numFmt numFmtId="170" formatCode="\₦#,##0"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3490,8 +3915,18 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="30">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3622,6 +4057,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF123D70"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF176AA1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCEAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -3644,7 +4105,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="137">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -3862,11 +4323,25 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -3882,9 +4357,6 @@
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4662,7 +5134,517 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1155700</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="AutoShape 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{748CCBC1-E9A2-886E-18E7-683BC29C17B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6350000" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1155700</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="AutoShape 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3B5BA85C-1AAE-047F-02B0-0081597DB149}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="6350000" cy="6350000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Overview"/>
+      <sheetName val="User_Inputs"/>
+      <sheetName val="Bill_Input"/>
+      <sheetName val="Appliance_Library"/>
+      <sheetName val="Appliance_Input"/>
+      <sheetName val="Custom_Equipment"/>
+      <sheetName val="Location_Assumptions"/>
+      <sheetName val="Location_Intelligence"/>
+      <sheetName val="Power_Path_Logic"/>
+      <sheetName val="Objective_Logic"/>
+      <sheetName val="Derived_Assumptions"/>
+      <sheetName val="Load_Estimation"/>
+      <sheetName val="Solar_Sizing"/>
+      <sheetName val="Battery_Sizing"/>
+      <sheetName val="Inverter_Sizing"/>
+      <sheetName val="Diesel_Economics"/>
+      <sheetName val="Financial_Model"/>
+      <sheetName val="Recommendation_Rules"/>
+      <sheetName val="Lead_Routing"/>
+      <sheetName val="Outputs"/>
+      <sheetName val="Formula_Map"/>
+      <sheetName val="Developer_Bridge"/>
+      <sheetName val="START_HERE"/>
+      <sheetName val="Customer_Scenario"/>
+      <sheetName val="Finance_Partners"/>
+      <sheetName val="Finance_Products"/>
+      <sheetName val="Finance_Matches"/>
+      <sheetName val="Partner_Choice"/>
+      <sheetName val="Finance_Enquiry"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23">
+        <row r="8">
+          <cell r="B8">
+            <v>6880000</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11">
+            <v>36</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>DEMO-F001</v>
+          </cell>
+          <cell r="D2" t="str">
+            <v>Asset financing</v>
+          </cell>
+          <cell r="L2">
+            <v>0.2</v>
+          </cell>
+          <cell r="M2">
+            <v>25000</v>
+          </cell>
+          <cell r="N2">
+            <v>500</v>
+          </cell>
+          <cell r="O2" t="str">
+            <v>Demo: ID, proof of address, income evidence, credit review and signed agreement.</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>DEMO-F002</v>
+          </cell>
+          <cell r="D3" t="str">
+            <v>Asset financing</v>
+          </cell>
+          <cell r="L3">
+            <v>0.22</v>
+          </cell>
+          <cell r="M3">
+            <v>30000</v>
+          </cell>
+          <cell r="N3">
+            <v>0</v>
+          </cell>
+          <cell r="O3" t="str">
+            <v>Demo: ID, proof of address, income evidence, credit review and signed agreement.</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>DEMO-F003</v>
+          </cell>
+          <cell r="D4" t="str">
+            <v>Energy-as-a-Service / lease</v>
+          </cell>
+          <cell r="L4"/>
+          <cell r="M4">
+            <v>35000</v>
+          </cell>
+          <cell r="N4">
+            <v>500</v>
+          </cell>
+          <cell r="O4" t="str">
+            <v>Demo: ID, address, income evidence; lender credit assessment. EaaS requires a separate usage-based quote.</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>DEMO-F004</v>
+          </cell>
+          <cell r="D5" t="str">
+            <v>Asset financing</v>
+          </cell>
+          <cell r="L5">
+            <v>0.26</v>
+          </cell>
+          <cell r="M5">
+            <v>40000</v>
+          </cell>
+          <cell r="N5">
+            <v>0</v>
+          </cell>
+          <cell r="O5" t="str">
+            <v>Demo: ID, proof of address, income evidence, credit review and signed agreement.</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>DEMO-F005</v>
+          </cell>
+          <cell r="D6" t="str">
+            <v>Solar instalment plan</v>
+          </cell>
+          <cell r="L6">
+            <v>0.28000000000000003</v>
+          </cell>
+          <cell r="M6">
+            <v>45000</v>
+          </cell>
+          <cell r="N6">
+            <v>500</v>
+          </cell>
+          <cell r="O6" t="str">
+            <v>Demo: ID, proof of address, income evidence, credit review and signed agreement.</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>DEMO-F006</v>
+          </cell>
+          <cell r="D7" t="str">
+            <v>Asset financing</v>
+          </cell>
+          <cell r="L7">
+            <v>0.18</v>
+          </cell>
+          <cell r="M7">
+            <v>50000</v>
+          </cell>
+          <cell r="N7">
+            <v>0</v>
+          </cell>
+          <cell r="O7" t="str">
+            <v>Demo: ID, proof of address, income evidence, credit review and signed agreement.</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>DEMO-F007</v>
+          </cell>
+          <cell r="D8" t="str">
+            <v>Solar instalment plan</v>
+          </cell>
+          <cell r="L8">
+            <v>0.2</v>
+          </cell>
+          <cell r="M8">
+            <v>55000</v>
+          </cell>
+          <cell r="N8">
+            <v>500</v>
+          </cell>
+          <cell r="O8" t="str">
+            <v>Demo: ID, proof of address, income evidence, credit review and signed agreement.</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>DEMO-F008</v>
+          </cell>
+          <cell r="D9" t="str">
+            <v>Energy-as-a-Service / lease</v>
+          </cell>
+          <cell r="L9"/>
+          <cell r="M9">
+            <v>60000</v>
+          </cell>
+          <cell r="N9">
+            <v>0</v>
+          </cell>
+          <cell r="O9" t="str">
+            <v>Demo: ID, address, income evidence; lender credit assessment. EaaS requires a separate usage-based quote.</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>DEMO-F009</v>
+          </cell>
+          <cell r="D10" t="str">
+            <v>Asset financing</v>
+          </cell>
+          <cell r="L10">
+            <v>0.24</v>
+          </cell>
+          <cell r="M10">
+            <v>65000</v>
+          </cell>
+          <cell r="N10">
+            <v>500</v>
+          </cell>
+          <cell r="O10" t="str">
+            <v>Demo: ID, proof of address, income evidence, credit review and signed agreement.</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>DEMO-F010</v>
+          </cell>
+          <cell r="D11" t="str">
+            <v>Asset financing</v>
+          </cell>
+          <cell r="L11">
+            <v>0.26</v>
+          </cell>
+          <cell r="M11">
+            <v>70000</v>
+          </cell>
+          <cell r="N11">
+            <v>0</v>
+          </cell>
+          <cell r="O11" t="str">
+            <v>Demo: ID, proof of address, income evidence, credit review and signed agreement.</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>DEMO-F011</v>
+          </cell>
+          <cell r="D12" t="str">
+            <v>Solar instalment plan</v>
+          </cell>
+          <cell r="L12">
+            <v>0.28000000000000003</v>
+          </cell>
+          <cell r="M12">
+            <v>75000</v>
+          </cell>
+          <cell r="N12">
+            <v>500</v>
+          </cell>
+          <cell r="O12" t="str">
+            <v>Demo: ID, proof of address, income evidence, credit review and signed agreement.</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>DEMO-F012</v>
+          </cell>
+          <cell r="D13" t="str">
+            <v>Energy-as-a-Service / lease</v>
+          </cell>
+          <cell r="L13"/>
+          <cell r="M13">
+            <v>80000</v>
+          </cell>
+          <cell r="N13">
+            <v>0</v>
+          </cell>
+          <cell r="O13" t="str">
+            <v>Demo: ID, address, income evidence; lender credit assessment. EaaS requires a separate usage-based quote.</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="26">
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>DEMO-F001</v>
+          </cell>
+          <cell r="K2">
+            <v>256185.45351501432</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>DEMO-F002</v>
+          </cell>
+          <cell r="K3"/>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>DEMO-F003</v>
+          </cell>
+          <cell r="K4"/>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>DEMO-F004</v>
+          </cell>
+          <cell r="K5">
+            <v>277199.46935941442</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>DEMO-F005</v>
+          </cell>
+          <cell r="K6"/>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>DEMO-F006</v>
+          </cell>
+          <cell r="K7">
+            <v>248728.48128710783</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>DEMO-F007</v>
+          </cell>
+          <cell r="K8"/>
+        </row>
+        <row r="9">
+          <cell r="A9" t="str">
+            <v>DEMO-F008</v>
+          </cell>
+          <cell r="K9"/>
+        </row>
+        <row r="10">
+          <cell r="A10" t="str">
+            <v>DEMO-F009</v>
+          </cell>
+          <cell r="K10">
+            <v>270422.02587285126</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11" t="str">
+            <v>DEMO-F010</v>
+          </cell>
+          <cell r="K11">
+            <v>277199.46935941442</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12" t="str">
+            <v>DEMO-F011</v>
+          </cell>
+          <cell r="K12"/>
+        </row>
+        <row r="13">
+          <cell r="A13" t="str">
+            <v>DEMO-F012</v>
+          </cell>
+          <cell r="K13"/>
+        </row>
+      </sheetData>
+      <sheetData sheetId="27"/>
+      <sheetData sheetId="28"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4908,18 +5890,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
-      <c r="A1" s="120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
+      <c r="A1" s="130" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
@@ -5018,28 +6000,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="130" t="s">
         <v>520</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="132" t="s">
         <v>521</v>
       </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
-      <c r="F3" s="119"/>
+      <c r="B3" s="131"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="131"/>
+      <c r="E3" s="131"/>
+      <c r="F3" s="131"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="13"/>
@@ -5239,10 +6221,10 @@
       <c r="G14" s="16"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="118"/>
-      <c r="B17" s="119"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="119"/>
+      <c r="A17" s="132"/>
+      <c r="B17" s="131"/>
+      <c r="C17" s="131"/>
+      <c r="D17" s="131"/>
       <c r="H17" s="95" t="s">
         <v>1016</v>
       </c>
@@ -5459,21 +6441,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="120"/>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
+      <c r="A1" s="130"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="118"/>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
+      <c r="A3" s="132"/>
+      <c r="B3" s="131"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="131"/>
+      <c r="E3" s="131"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1"/>
@@ -5493,7 +6475,7 @@
       <c r="A6" s="1"/>
       <c r="B6" s="101">
         <f>Appliance_Input!L5</f>
-        <v>2893.5</v>
+        <v>401.92499999999995</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -5507,35 +6489,35 @@
       <c r="A8" s="1"/>
       <c r="B8" s="101">
         <f>IFERROR(CHOOSE(MATCH(B4,{"Bill","Appliances","Custom"},0),B5,B6,B7),0)</f>
-        <v>2893.5</v>
+        <v>401.92499999999995</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1"/>
       <c r="B9" s="98">
         <f>B8*12</f>
-        <v>34722</v>
+        <v>4823.0999999999995</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1"/>
       <c r="B10" s="101">
         <f>IF(B4="Bill",IF(User_Inputs!B19&gt;0,User_Inputs!B19,B8/(30*24)*3),IF(B4="Appliances",Appliance_Input!L6,IF(B4="Custom",Custom_Equipment!M7,0)))</f>
-        <v>16.8</v>
+        <v>3.7725</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1"/>
       <c r="B11" s="101">
         <f>IF(User_Inputs!B19&gt;0,User_Inputs!B19,B10)</f>
-        <v>16.8</v>
+        <v>3.7725</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1"/>
       <c r="B12" s="101">
         <f>B11*User_Inputs!B24</f>
-        <v>10.08</v>
+        <v>2.2635000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -5560,16 +6542,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="130" t="s">
         <v>530</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1"/>
@@ -5582,14 +6564,14 @@
       <c r="A5" s="1"/>
       <c r="B5" s="101">
         <f>Load_Estimation!B12</f>
-        <v>10.08</v>
+        <v>2.2635000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1"/>
       <c r="B6" s="101">
         <f>User_Inputs!B25</f>
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -5603,35 +6585,35 @@
       <c r="A8" s="1"/>
       <c r="B8" s="101">
         <f>B5*B6</f>
-        <v>80.64</v>
+        <v>9.0540000000000003</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1"/>
       <c r="B9" s="101">
         <f>B8</f>
-        <v>80.64</v>
+        <v>9.0540000000000003</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1"/>
       <c r="B10" s="101">
         <f>IF(MIN(MAX(2,B9/(1-User_Inputs!B27)),User_Inputs!F43)&lt;=Assumptions!H18,Assumptions!H18,IF(MIN(MAX(2,B9/(1-User_Inputs!B27)),User_Inputs!F43)&lt;=Assumptions!H19,Assumptions!H19,IF(MIN(MAX(2,B9/(1-User_Inputs!B27)),User_Inputs!F43)&lt;=Assumptions!H20,Assumptions!H20,IF(MIN(MAX(2,B9/(1-User_Inputs!B27)),User_Inputs!F43)&lt;=Assumptions!H21,Assumptions!H21,IF(MIN(MAX(2,B9/(1-User_Inputs!B27)),User_Inputs!F43)&lt;=Assumptions!H22,Assumptions!H22,IF(MIN(MAX(2,B9/(1-User_Inputs!B27)),User_Inputs!F43)&lt;=Assumptions!H23,Assumptions!H23,IF(MIN(MAX(2,B9/(1-User_Inputs!B27)),User_Inputs!F43)&lt;=Assumptions!H24,Assumptions!H24,IF(MIN(MAX(2,B9/(1-User_Inputs!B27)),User_Inputs!F43)&lt;=Assumptions!H25,Assumptions!H25,IF(MIN(MAX(2,B9/(1-User_Inputs!B27)),User_Inputs!F43)&lt;=Assumptions!H26,Assumptions!H26,IF(MIN(MAX(2,B9/(1-User_Inputs!B27)),User_Inputs!F43)&lt;=Assumptions!H27,Assumptions!H27,IF(MIN(MAX(2,B9/(1-User_Inputs!B27)),User_Inputs!F43)&lt;=Assumptions!H28,Assumptions!H28,IF(MIN(MAX(2,B9/(1-User_Inputs!B27)),User_Inputs!F43)&lt;=Assumptions!H29,Assumptions!H29,IF(MIN(MAX(2,B9/(1-User_Inputs!B27)),User_Inputs!F43)&lt;=Assumptions!H30,Assumptions!H30,IF(MIN(MAX(2,B9/(1-User_Inputs!B27)),User_Inputs!F43)&lt;=Assumptions!H31,Assumptions!H31,IF(MIN(MAX(2,B9/(1-User_Inputs!B27)),User_Inputs!F43)&lt;=Assumptions!H32,Assumptions!H32,User_Inputs!F43)))))))))))))))</f>
-        <v>120</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1"/>
       <c r="B11" s="101">
         <f>Load_Estimation!B11*User_Inputs!B44</f>
-        <v>20.16</v>
+        <v>4.5270000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1"/>
       <c r="B12" s="101">
         <f>IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I18,Assumptions!I18,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I19,Assumptions!I19,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I20,Assumptions!I20,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I21,Assumptions!I21,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I22,Assumptions!I22,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I23,Assumptions!I23,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I24,Assumptions!I24,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I25,Assumptions!I25,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I26,Assumptions!I26,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I27,Assumptions!I27,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I28,Assumptions!I28,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I29,Assumptions!I29,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I30,Assumptions!I30,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I31,Assumptions!I31,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I32,Assumptions!I32,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I33,Assumptions!I33,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I34,Assumptions!I34,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I35,Assumptions!I35,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I36,Assumptions!I36,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I37,Assumptions!I37,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I38,Assumptions!I38,IF(MIN(MAX(1,B11),User_Inputs!F44)&lt;=Assumptions!I39,Assumptions!I39,User_Inputs!F44))))))))))))))))))))))</f>
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -5648,14 +6630,14 @@
       <c r="A16" s="1"/>
       <c r="B16" s="103">
         <f>MAX(B9,2)</f>
-        <v>80.64</v>
+        <v>9.0540000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="102">
         <f>IF(CEILING((B9/(1-User_Inputs!B27)),0.5)&lt;=2,2,IF(CEILING((B9/(1-User_Inputs!B27)),0.5)&lt;=5,5,IF(CEILING((B9/(1-User_Inputs!B27)),0.5)&lt;=7.5,7.5,IF(CEILING((B9/(1-User_Inputs!B27)),0.5)&lt;=10,10,IF(CEILING((B9/(1-User_Inputs!B27)),0.5)&lt;=15,15,IF(CEILING((B9/(1-User_Inputs!B27)),0.5)&lt;=20,20,IF(CEILING((B9/(1-User_Inputs!B27)),0.5)&lt;=30,30,50)))))))</f>
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -5668,7 +6650,7 @@
       <c r="A20" s="1"/>
       <c r="B20" s="101">
         <f>CEILING((B9/(1-User_Inputs!B27)),0.5)</f>
-        <v>101</v>
+        <v>11.5</v>
       </c>
       <c r="C20" s="31"/>
     </row>
@@ -5676,7 +6658,7 @@
       <c r="A21" s="1"/>
       <c r="B21" s="101">
         <f>ROUNDUP(B11/0.5,0)*0.5</f>
-        <v>20.5</v>
+        <v>5</v>
       </c>
       <c r="C21" s="31"/>
     </row>
@@ -5704,14 +6686,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="120"/>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
+      <c r="A1" s="130"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1"/>
@@ -5724,7 +6706,7 @@
       <c r="A5" s="1"/>
       <c r="B5" s="98">
         <f>Load_Estimation!B9</f>
-        <v>34722</v>
+        <v>4823.0999999999995</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -5745,7 +6727,7 @@
       <c r="A8" s="1"/>
       <c r="B8" s="98">
         <f>B5*B7</f>
-        <v>31249.8</v>
+        <v>4340.79</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -5766,14 +6748,14 @@
       <c r="A11" s="1"/>
       <c r="B11" s="101">
         <f>IFERROR(B8/(User_Inputs!B42*User_Inputs!B43),0)</f>
-        <v>28.735448275862069</v>
+        <v>3.9915310344827586</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1"/>
       <c r="B12" s="101">
         <f>IF(OR(B20&lt;=0,B17&lt;=0),0,MIN(CEILING(B11*1000/B20,1),FLOOR(B17*1000/B20,1))*B20/1000)</f>
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
@@ -5784,14 +6766,14 @@
       <c r="A13" s="1"/>
       <c r="B13" s="98">
         <f>B12*User_Inputs!B42</f>
-        <v>42050</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1"/>
       <c r="B14" s="98">
         <f>MIN(B13*User_Inputs!B43,B5)</f>
-        <v>31537.5</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -5822,7 +6804,7 @@
     <row r="21" spans="1:2">
       <c r="B21" s="102">
         <f>IF(B20&gt;0,ROUND(B12*1000/B20,0),0)</f>
-        <v>58</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -5855,20 +6837,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="120"/>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
+      <c r="A1" s="130"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="106"/>
       <c r="B4" s="107">
         <f>Solar_Sizing!B12*User_Inputs!B33</f>
-        <v>15950000</v>
+        <v>1200000</v>
       </c>
       <c r="C4" s="102"/>
       <c r="D4" s="108" t="s">
@@ -5883,7 +6865,7 @@
       <c r="A5" s="106"/>
       <c r="B5" s="107">
         <f>Battery_Sizing!B10*User_Inputs!B34</f>
-        <v>50400000</v>
+        <v>3900000</v>
       </c>
       <c r="C5" s="102"/>
       <c r="D5" s="102"/>
@@ -5896,7 +6878,7 @@
       <c r="A6" s="106"/>
       <c r="B6" s="107">
         <f>Battery_Sizing!B12*User_Inputs!B35</f>
-        <v>9500000</v>
+        <v>1150000</v>
       </c>
       <c r="C6" s="102"/>
       <c r="D6" s="102"/>
@@ -5909,7 +6891,7 @@
       <c r="A7" s="106"/>
       <c r="B7" s="107">
         <f>SUM(B4:B6)</f>
-        <v>75850000</v>
+        <v>6250000</v>
       </c>
       <c r="C7" s="102"/>
       <c r="D7" s="102"/>
@@ -5922,7 +6904,7 @@
       <c r="A8" s="106"/>
       <c r="B8" s="107">
         <f>B7*User_Inputs!B36</f>
-        <v>15170000</v>
+        <v>750000</v>
       </c>
       <c r="C8" s="102"/>
       <c r="D8" s="102"/>
@@ -5935,7 +6917,7 @@
       <c r="A9" s="106"/>
       <c r="B9" s="107">
         <f>B7+B8</f>
-        <v>91020000</v>
+        <v>7000000</v>
       </c>
       <c r="C9" s="102"/>
       <c r="D9" s="102"/>
@@ -5948,7 +6930,7 @@
       <c r="A10" s="106"/>
       <c r="B10" s="107">
         <f>Diesel_Economics!B24*User_Inputs!B30 + Diesel_Economics!B8*Diesel_Economics!B6</f>
-        <v>6607106.25</v>
+        <v>1072123.7089285715</v>
       </c>
       <c r="C10" s="102"/>
       <c r="D10" s="102"/>
@@ -5961,7 +6943,7 @@
       <c r="A11" s="106"/>
       <c r="B11" s="107">
         <f>B9*User_Inputs!B37</f>
-        <v>1820400</v>
+        <v>140000</v>
       </c>
       <c r="C11" s="102"/>
       <c r="D11" s="102"/>
@@ -5974,7 +6956,7 @@
       <c r="A12" s="106"/>
       <c r="B12" s="107">
         <f>B10-B11</f>
-        <v>4786706.25</v>
+        <v>932123.70892857155</v>
       </c>
       <c r="C12" s="102"/>
       <c r="D12" s="102"/>
@@ -5987,7 +6969,7 @@
       <c r="A13" s="106"/>
       <c r="B13" s="109">
         <f>IF(B12&gt;0,B9/B12,"")</f>
-        <v>19.015163088397163</v>
+        <v>7.5097328100860574</v>
       </c>
       <c r="C13" s="102"/>
       <c r="D13" s="102"/>
@@ -6007,20 +6989,20 @@
       <c r="H14" s="102"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="121"/>
-      <c r="B15" s="122"/>
-      <c r="C15" s="122"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="122"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="122"/>
-      <c r="H15" s="122"/>
+      <c r="A15" s="133"/>
+      <c r="B15" s="134"/>
+      <c r="C15" s="134"/>
+      <c r="D15" s="134"/>
+      <c r="E15" s="134"/>
+      <c r="F15" s="134"/>
+      <c r="G15" s="134"/>
+      <c r="H15" s="134"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="110"/>
       <c r="B16" s="102">
         <f>IFERROR((B20*B22+B21)/B23,0)</f>
-        <v>138.73152884228384</v>
+        <v>86.682221131907681</v>
       </c>
       <c r="C16" s="111" t="s">
         <v>1001</v>
@@ -6075,7 +7057,7 @@
       <c r="A20" s="112"/>
       <c r="B20" s="102">
         <f>(B4+B6)*(1+User_Inputs!B36)</f>
-        <v>30540000</v>
+        <v>2632000.0000000005</v>
       </c>
       <c r="C20" s="102"/>
       <c r="D20" s="102"/>
@@ -6088,7 +7070,7 @@
       <c r="A21" s="112"/>
       <c r="B21" s="102">
         <f>B20*User_Inputs!B37</f>
-        <v>610800</v>
+        <v>52640.000000000007</v>
       </c>
       <c r="C21" s="102"/>
       <c r="D21" s="102"/>
@@ -6114,7 +7096,7 @@
       <c r="A23" s="112"/>
       <c r="B23" s="105">
         <f>Solar_Sizing!B13</f>
-        <v>42050</v>
+        <v>5800</v>
       </c>
       <c r="C23" s="102"/>
       <c r="D23" s="102"/>
@@ -6144,16 +7126,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
-      <c r="A1" s="120"/>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
+      <c r="A1" s="130"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="13"/>
@@ -6291,50 +7273,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
-      <c r="A1" s="120"/>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
+      <c r="A1" s="130"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1"/>
       <c r="B4" s="19" t="str">
         <f>IF(Solar_Sizing!B12&lt;5,"Small",IF(Solar_Sizing!B12&lt;30,"Medium","Large"))</f>
-        <v>Medium</v>
+        <v>Small</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="1"/>
       <c r="B5" s="20">
         <f>IF(User_Inputs!B10="Hospital",2,0)+IF(User_Inputs!B13="Grid + Generator",2,0)+IF(User_Inputs!B20&gt;=6,1,0)+IF(Battery_Sizing!B10&gt;=50,1,0)+IF(User_Inputs!B15="Custom",2,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="1"/>
       <c r="B6" s="19" t="str">
         <f>IF(B5&gt;=5,"Complex / SAEK",IF(AND(User_Inputs!B10="Home",Solar_Sizing!B12&lt;10),"Residential / Installer","SME / Review"))</f>
-        <v>SME / Review</v>
+        <v>Residential / Installer</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="1"/>
       <c r="B7" s="19" t="str">
         <f>IF(B6="Complex / SAEK","Route to SAEK advisory",IF(B6="Residential / Installer","Match to installer / supplier","Offer quotes + detailed review"))</f>
-        <v>Offer quotes + detailed review</v>
+        <v>Match to installer / supplier</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="1"/>
       <c r="B8" s="19" t="str">
         <f>IF(Financial_Model!B9&gt;=50000000,"High",IF(Financial_Model!B9&gt;=10000000,"Medium","Standard"))</f>
-        <v>High</v>
+        <v>Standard</v>
       </c>
     </row>
   </sheetData>
@@ -6357,27 +7339,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="120"/>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
+      <c r="A1" s="130"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1"/>
       <c r="B4" s="97" t="str">
         <f>User_Inputs!B13</f>
-        <v>Grid Only</v>
+        <v>Grid + Generator</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1"/>
       <c r="B5" s="100">
         <f>MIN(1,User_Inputs!B20/24)</f>
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -6391,21 +7373,21 @@
       <c r="A7" s="1"/>
       <c r="B7" s="113">
         <f>IF(B4="Grid Only",User_Inputs!B30,User_Inputs!B30*(1-B5)+B6*B5)</f>
-        <v>209.5</v>
+        <v>242.83928571428572</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1"/>
       <c r="B8" s="98">
         <f>IF(B4="Grid + Generator",MIN(B11,B19+B23),IF(B4="Generator Only",MIN(B11,Solar_Sizing!B14),0))</f>
-        <v>0</v>
+        <v>1205.7749999999999</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1"/>
       <c r="B9" s="101">
         <f>IFERROR(B8/User_Inputs!B32,0)</f>
-        <v>0</v>
+        <v>344.50714285714281</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -6415,13 +7397,13 @@
       <c r="A11" s="44"/>
       <c r="B11" s="105">
         <f>IF(B4="Grid Only",0,IF(B4="Generator Only",Load_Estimation!B9,Load_Estimation!B9*B5))</f>
-        <v>0</v>
+        <v>1205.7749999999999</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="B12" s="102">
         <f>IF(B4="Generator Only",0,IF(B4="Grid Only",Load_Estimation!B9,Load_Estimation!B9*(1-B5)))</f>
-        <v>34722</v>
+        <v>3617.3249999999998</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -6435,67 +7417,67 @@
     <row r="15" spans="1:8">
       <c r="B15" s="114">
         <f>Load_Estimation!B11*B14</f>
-        <v>21</v>
+        <v>4.7156250000000002</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="B16" s="114">
         <f>B15/0.8</f>
-        <v>26.25</v>
+        <v>5.89453125</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="114">
         <f>B16</f>
-        <v>26.25</v>
+        <v>5.89453125</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" s="114">
         <f>IF(B17&lt;=5,5,IF(B17&lt;=7.5,7.5,IF(B17&lt;=10,10,IF(B17&lt;=12.5,12.5,IF(B17&lt;=15,15,IF(B17&lt;=20,20,IF(B17&lt;=25,25,IF(B17&lt;=30,30,IF(B17&lt;=40,40,IF(B17&lt;=50,50,IF(B17&lt;=60,60,IF(B17&lt;=80,80,IF(B17&lt;=100,100,IF(B17&lt;=125,125,IF(B17&lt;=150,150,IF(B17&lt;=200,200,IF(B17&lt;=250,250,IF(B17&lt;=300,300,IF(B17&lt;=400,400,500)))))))))))))))))))</f>
-        <v>30</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" s="114">
         <f>IF(B4="Grid + Generator",MIN(B11,Solar_Sizing!B14*B5),IF(B4="Generator Only",MIN(B11,Solar_Sizing!B14),0))</f>
-        <v>0</v>
+        <v>1087.5</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="102">
         <f>IF(B4="Grid + Generator",MIN(B12,Solar_Sizing!B14*(1-B5)),IF(B4="Grid Only",MIN(B12,Solar_Sizing!B14),0))</f>
-        <v>31537.5</v>
+        <v>3262.5</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="102">
         <f>Battery_Sizing!B10*(1-User_Inputs!B27)</f>
-        <v>96</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" s="102">
         <f>B21*365</f>
-        <v>35040</v>
+        <v>4380</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" s="102">
         <f>IF(B4&lt;&gt;"Grid + Generator",0,MIN(MAX(0,B11-B19),B20,B22)*IF(User_Inputs!B14="Reduce Diesel Use",1,IF(User_Inputs!B14="Backup During Outages",1,IF(User_Inputs!B14="Balanced",0.5,0))))</f>
-        <v>0</v>
+        <v>118.27499999999986</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="102">
         <f>IF(B4="Grid + Generator",MAX(0,B20-B23),IF(B4="Grid Only",B20,0))</f>
-        <v>31537.5</v>
+        <v>3144.2250000000004</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" s="102">
         <f>B24+B8</f>
-        <v>31537.5</v>
+        <v>4350</v>
       </c>
     </row>
   </sheetData>
@@ -6522,16 +7504,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="130" t="s">
         <v>553</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
@@ -6566,7 +7548,7 @@
       </c>
       <c r="B7" s="21" t="str">
         <f>User_Inputs!B10</f>
-        <v>Hotel</v>
+        <v>Home</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -6575,7 +7557,7 @@
       </c>
       <c r="B8" s="21" t="str">
         <f>User_Inputs!B13</f>
-        <v>Grid Only</v>
+        <v>Grid + Generator</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -6593,7 +7575,7 @@
       </c>
       <c r="B10" s="22">
         <f>Solar_Sizing!B12</f>
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
         <v>559</v>
@@ -6605,7 +7587,7 @@
       </c>
       <c r="B11" s="22">
         <f>Battery_Sizing!B10</f>
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
         <v>561</v>
@@ -6617,7 +7599,7 @@
       </c>
       <c r="B12" s="22">
         <f>Battery_Sizing!B12</f>
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C12" t="s">
         <v>563</v>
@@ -6629,7 +7611,7 @@
       </c>
       <c r="B13" s="23">
         <f>Solar_Sizing!B13</f>
-        <v>42050</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -6638,7 +7620,7 @@
       </c>
       <c r="B14" s="23">
         <f>Solar_Sizing!B14</f>
-        <v>31537.5</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -6647,7 +7629,7 @@
       </c>
       <c r="B15" s="24">
         <f>Financial_Model!B9</f>
-        <v>91020000</v>
+        <v>7000000</v>
       </c>
       <c r="C15" t="s">
         <v>534</v>
@@ -6659,7 +7641,7 @@
       </c>
       <c r="B16" s="24">
         <f>Financial_Model!B10</f>
-        <v>6607106.25</v>
+        <v>1072123.7089285715</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6668,7 +7650,7 @@
       </c>
       <c r="B17" s="24">
         <f>Financial_Model!B11</f>
-        <v>1820400</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6677,7 +7659,7 @@
       </c>
       <c r="B18" s="24">
         <f>Financial_Model!B12</f>
-        <v>4786706.25</v>
+        <v>932123.70892857155</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6686,7 +7668,7 @@
       </c>
       <c r="B19" s="25">
         <f>Financial_Model!B13</f>
-        <v>19.015163088397163</v>
+        <v>7.5097328100860574</v>
       </c>
       <c r="C19" t="s">
         <v>568</v>
@@ -6698,7 +7680,7 @@
       </c>
       <c r="B20" s="22">
         <f>Diesel_Economics!B9</f>
-        <v>0</v>
+        <v>344.50714285714281</v>
       </c>
       <c r="C20" t="s">
         <v>570</v>
@@ -6710,7 +7692,7 @@
       </c>
       <c r="B21" s="21" t="str">
         <f>Lead_Routing!B6</f>
-        <v>SME / Review</v>
+        <v>Residential / Installer</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6719,7 +7701,7 @@
       </c>
       <c r="B22" s="21" t="str">
         <f>Lead_Routing!B7</f>
-        <v>Offer quotes + detailed review</v>
+        <v>Match to installer / supplier</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6755,7 +7737,7 @@
       </c>
       <c r="B27" s="54">
         <f>IFERROR(Solar_Sizing!B14/Load_Estimation!B9,0)</f>
-        <v>0.90828581302920341</v>
+        <v>0.90190956024133861</v>
       </c>
       <c r="C27" t="s">
         <v>939</v>
@@ -6767,7 +7749,7 @@
       </c>
       <c r="B28" s="54">
         <f>IFERROR(Diesel_Economics!B24/Diesel_Economics!B12,0)</f>
-        <v>0.90828581302920341</v>
+        <v>0.86921274698845152</v>
       </c>
       <c r="C28" t="s">
         <v>940</v>
@@ -6779,7 +7761,7 @@
       </c>
       <c r="B29" s="54">
         <f>IFERROR(Diesel_Economics!B8/Diesel_Economics!B11,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" t="s">
         <v>941</v>
@@ -6791,7 +7773,7 @@
       </c>
       <c r="B31" s="54" t="str">
         <f>IF(B12&lt;3.5,"Class A",IF(B12&lt;5,"Class B",IF(B12&lt;10,"Class C",IF(B12&lt;50,"Class D","Class E"))))</f>
-        <v>Class D</v>
+        <v>Class C</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6805,7 +7787,7 @@
       </c>
       <c r="B34" s="60">
         <f>Load_Estimation!B9</f>
-        <v>34722</v>
+        <v>4823.0999999999995</v>
       </c>
       <c r="C34" t="s">
         <v>561</v>
@@ -6843,7 +7825,7 @@
       </c>
       <c r="B39" s="63">
         <f>Appliance_Input!L4</f>
-        <v>96.45</v>
+        <v>13.397500000000003</v>
       </c>
       <c r="C39" t="s">
         <v>561</v>
@@ -6855,7 +7837,7 @@
       </c>
       <c r="B40" s="64">
         <f>Appliance_Input!L5</f>
-        <v>2893.5</v>
+        <v>401.92499999999995</v>
       </c>
       <c r="C40" t="s">
         <v>561</v>
@@ -6867,7 +7849,7 @@
       </c>
       <c r="B41" s="60">
         <f>Load_Estimation!B9</f>
-        <v>34722</v>
+        <v>4823.0999999999995</v>
       </c>
       <c r="C41" t="s">
         <v>561</v>
@@ -6908,7 +7890,7 @@
       </c>
       <c r="B46" s="60">
         <f>Load_Estimation!B9</f>
-        <v>34722</v>
+        <v>4823.0999999999995</v>
       </c>
       <c r="C46" t="s">
         <v>561</v>
@@ -6936,40 +7918,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="135" t="s">
         <v>942</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="123"/>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
-      <c r="J1" s="123"/>
-      <c r="K1" s="123"/>
-      <c r="L1" s="123"/>
-      <c r="M1" s="123"/>
-      <c r="N1" s="123"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
+      <c r="F1" s="135"/>
+      <c r="G1" s="135"/>
+      <c r="H1" s="135"/>
+      <c r="I1" s="135"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="135"/>
+      <c r="L1" s="135"/>
+      <c r="M1" s="135"/>
+      <c r="N1" s="135"/>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="124" t="s">
+      <c r="A2" s="136" t="s">
         <v>943</v>
       </c>
-      <c r="B2" s="124"/>
-      <c r="C2" s="124"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="124"/>
+      <c r="B2" s="136"/>
+      <c r="C2" s="136"/>
+      <c r="D2" s="136"/>
+      <c r="E2" s="136"/>
+      <c r="F2" s="136"/>
+      <c r="G2" s="136"/>
+      <c r="H2" s="136"/>
+      <c r="I2" s="136"/>
+      <c r="J2" s="136"/>
+      <c r="K2" s="136"/>
+      <c r="L2" s="136"/>
+      <c r="M2" s="136"/>
+      <c r="N2" s="136"/>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="30"/>
@@ -7037,7 +8019,7 @@
       </c>
       <c r="B5" s="67">
         <f>G5*User_Inputs!B30</f>
-        <v>3637129.5</v>
+        <v>757829.58749999991</v>
       </c>
       <c r="C5" s="30" t="str">
         <f>IF(User_Inputs!B20=0,"Very High",IF(User_Inputs!B20&lt;=1,"High",IF(User_Inputs!B20&lt;=4,"Medium","Low")))</f>
@@ -7055,7 +8037,7 @@
       </c>
       <c r="G5" s="69">
         <f>Load_Estimation!B9*(1-MIN(1,MAX(0,User_Inputs!B20/24)))</f>
-        <v>17361</v>
+        <v>3617.3249999999998</v>
       </c>
       <c r="H5" s="69">
         <v>0</v>
@@ -7085,7 +8067,7 @@
       </c>
       <c r="B6" s="67">
         <f>G6*User_Inputs!B30+H6*(User_Inputs!B31/User_Inputs!B32)</f>
-        <v>9589472.3571428563</v>
+        <v>1171238.1589285713</v>
       </c>
       <c r="C6" s="30" t="s">
         <v>960</v>
@@ -7103,15 +8085,15 @@
       </c>
       <c r="G6" s="69">
         <f>Load_Estimation!B9*(1-MIN(1,MAX(0,User_Inputs!B20/24)))</f>
-        <v>17361</v>
+        <v>3617.3249999999998</v>
       </c>
       <c r="H6" s="69">
         <f>Load_Estimation!B9*MIN(1,MAX(0,User_Inputs!B20/24))</f>
-        <v>17361</v>
+        <v>1205.7749999999999</v>
       </c>
       <c r="I6" s="69">
         <f>IFERROR(H6/User_Inputs!B32,0)</f>
-        <v>4960.2857142857147</v>
+        <v>344.50714285714281</v>
       </c>
       <c r="J6" s="69">
         <v>0</v>
@@ -7135,7 +8117,7 @@
       </c>
       <c r="B7" s="67">
         <f>G7*User_Inputs!B30+K7</f>
-        <v>944376.375</v>
+        <v>126975.83749999997</v>
       </c>
       <c r="C7" s="30" t="str">
         <f>IF(User_Inputs!B20=0,"Very High",IF(Solar_Sizing!B14*MIN(1,MAX(0,User_Inputs!B20/24))&gt;=0.5*Load_Estimation!B9*MIN(1,MAX(0,User_Inputs!B20/24)),"Medium","Low"))</f>
@@ -7146,7 +8128,7 @@
       </c>
       <c r="E7" s="68">
         <f>IF(L7&gt;0,J7/L7,"—")</f>
-        <v>11.341552152130545</v>
+        <v>4.1721238876681008</v>
       </c>
       <c r="F7" s="30" t="str">
         <f>IF(User_Inputs!B14="Reduce Bills",IF(ROW()=IF(IFERROR($E$7,999)&lt;=IFERROR($E$8,999),7,8),"Recommended",""),IF(OR(User_Inputs!B14="Reduce Diesel Use",User_Inputs!B14="Backup During Outages",User_Inputs!B14="Balanced"),IF(ROW()=8,"Recommended",""),""))</f>
@@ -7154,7 +8136,7 @@
       </c>
       <c r="G7" s="69">
         <f>MAX(0,G5-MIN(G5,Solar_Sizing!B14*(1-MIN(1,MAX(0,User_Inputs!B20/24)))))</f>
-        <v>1592.25</v>
+        <v>354.82499999999982</v>
       </c>
       <c r="H7" s="69">
         <v>0</v>
@@ -7164,15 +8146,15 @@
       </c>
       <c r="J7" s="69">
         <f>Solar_Sizing!B12*User_Inputs!B33+Battery_Sizing!B12*User_Inputs!B35+(Solar_Sizing!B12*User_Inputs!B33+Battery_Sizing!B12*User_Inputs!B35)*User_Inputs!B36</f>
-        <v>30540000</v>
+        <v>2632000</v>
       </c>
       <c r="K7" s="69">
         <f>J7*User_Inputs!B37</f>
-        <v>610800</v>
+        <v>52640</v>
       </c>
       <c r="L7" s="69">
         <f>MAX(0,B5-B7)</f>
-        <v>2692753.125</v>
+        <v>630853.75</v>
       </c>
       <c r="M7" s="70">
         <v>0</v>
@@ -7187,7 +8169,7 @@
       </c>
       <c r="B8" s="72">
         <f>G8*User_Inputs!B30+H8*(User_Inputs!B31/User_Inputs!B32)+K8</f>
-        <v>2487552.75</v>
+        <v>239114.4499999999</v>
       </c>
       <c r="C8" s="71" t="s">
         <v>965</v>
@@ -7198,7 +8180,7 @@
       </c>
       <c r="E8" s="73">
         <f>IF(L8&gt;0,J8/L8,"—")</f>
-        <v>12.816253215321579</v>
+        <v>7.5097328100860592</v>
       </c>
       <c r="F8" s="71" t="str">
         <f>IF(User_Inputs!B14="Reduce Bills",IF(ROW()=IF(IFERROR($E$7,999)&lt;=IFERROR($E$8,999),7,8),"Recommended",""),IF(OR(User_Inputs!B14="Reduce Diesel Use",User_Inputs!B14="Backup During Outages",User_Inputs!B14="Balanced"),IF(ROW()=8,"Recommended",""),""))</f>
@@ -7206,7 +8188,7 @@
       </c>
       <c r="G8" s="74">
         <f>MAX(0,Diesel_Economics!B12-Diesel_Economics!B24)</f>
-        <v>3184.5</v>
+        <v>473.09999999999945</v>
       </c>
       <c r="H8" s="74">
         <f>MAX(0,Diesel_Economics!B11-Diesel_Economics!B8)</f>
@@ -7218,15 +8200,15 @@
       </c>
       <c r="J8" s="74">
         <f>Financial_Model!B9</f>
-        <v>91020000</v>
+        <v>7000000</v>
       </c>
       <c r="K8" s="74">
         <f>Financial_Model!B11</f>
-        <v>1820400</v>
+        <v>140000</v>
       </c>
       <c r="L8" s="74">
         <f>MAX(0,B6-B8)</f>
-        <v>7101919.6071428563</v>
+        <v>932123.70892857132</v>
       </c>
       <c r="M8" s="75">
         <f>IFERROR(1-H8/H6,0)</f>
@@ -7302,19 +8284,19 @@
       </c>
       <c r="B12" s="67">
         <f>B5</f>
-        <v>3637129.5</v>
+        <v>757829.58749999991</v>
       </c>
       <c r="C12" s="67">
         <f>B6</f>
-        <v>9589472.3571428563</v>
+        <v>1171238.1589285713</v>
       </c>
       <c r="D12" s="67">
         <f>B7</f>
-        <v>944376.375</v>
+        <v>126975.83749999997</v>
       </c>
       <c r="E12" s="67">
         <f>B8</f>
-        <v>2487552.75</v>
+        <v>239114.4499999999</v>
       </c>
       <c r="F12" s="30" t="s">
         <v>969</v>
@@ -7406,11 +8388,11 @@
       </c>
       <c r="D15" s="30">
         <f>E7</f>
-        <v>11.341552152130545</v>
+        <v>4.1721238876681008</v>
       </c>
       <c r="E15" s="30">
         <f>E8</f>
-        <v>12.816253215321579</v>
+        <v>7.5097328100860592</v>
       </c>
       <c r="F15" s="30" t="s">
         <v>972</v>
@@ -7466,7 +8448,7 @@
       </c>
       <c r="C17" s="76">
         <f>I6</f>
-        <v>4960.2857142857147</v>
+        <v>344.50714285714281</v>
       </c>
       <c r="D17" s="76">
         <f>I7</f>
@@ -7521,24 +8503,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="24" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="132" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
+      <c r="B3" s="131"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="131"/>
       <c r="I3" s="45" t="s">
         <v>4</v>
       </c>
@@ -7680,7 +8662,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I8" t="s">
         <v>34</v>
@@ -7736,7 +8718,7 @@
         <v>42</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
         <v>43</v>
@@ -7768,11 +8750,11 @@
         <v>48</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="C11" t="str">
         <f>B11</f>
-        <v>Medium Hotel - 25 Rooms Critical Loads</v>
+        <v>3-Bedroom House</v>
       </c>
       <c r="D11">
         <f>IF(C11="Studio / Self-contained",1,
@@ -7810,7 +8792,7 @@
 IF(C11="Computer Lab / Training Centre",37,
 IF(C11="Training Centre / Office",38,
 IF(C11="Church / Mosque / Event Hall",39,IF(C11="Boarding School Common Services",40))))))))))))))))))))))))))))))))))))))))</f>
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I11" t="s">
         <v>49</v>
@@ -7865,7 +8847,7 @@
         <v>58</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>956</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
         <v>60</v>
@@ -7980,12 +8962,12 @@
       </c>
     </row>
     <row r="17" spans="1:18">
-      <c r="A17" s="118" t="s">
+      <c r="A17" s="132" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="119"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="119"/>
+      <c r="B17" s="131"/>
+      <c r="C17" s="131"/>
+      <c r="D17" s="131"/>
       <c r="I17" t="s">
         <v>78</v>
       </c>
@@ -8069,14 +9051,14 @@
       </c>
       <c r="B20" s="5">
         <f>D20</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C20" t="s">
         <v>95</v>
       </c>
       <c r="D20">
-        <f>LOOKUP(B61,{"0-2 hours","3-6 hours","7-12 hours","13-18 hours","19-24 hours"},{2,6,12,18,24})</f>
-        <v>12</v>
+        <f>LOOKUP(B61,{"0-2 hours","2-6 hours","6-12 hours","12-18 hours","18-24 hours"},{2,6,12,18,24})</f>
+        <v>6</v>
       </c>
       <c r="I20" t="s">
         <v>96</v>
@@ -8221,7 +9203,7 @@
         <v>115</v>
       </c>
       <c r="B25" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
         <v>116</v>
@@ -8327,12 +9309,12 @@
       </c>
     </row>
     <row r="29" spans="1:18">
-      <c r="A29" s="118" t="s">
+      <c r="A29" s="132" t="s">
         <v>129</v>
       </c>
-      <c r="B29" s="119"/>
-      <c r="C29" s="119"/>
-      <c r="D29" s="119"/>
+      <c r="B29" s="131"/>
+      <c r="C29" s="131"/>
+      <c r="D29" s="131"/>
       <c r="I29" t="s">
         <v>130</v>
       </c>
@@ -8459,7 +9441,7 @@
       </c>
       <c r="B33" s="8">
         <f>IF($B$10="Home", 300000,IF($B$10="Office",420000,IF($B$10="Factory",320000,550000)))</f>
-        <v>550000</v>
+        <v>300000</v>
       </c>
       <c r="C33" s="31"/>
       <c r="E33" s="31" t="s">
@@ -8494,7 +9476,7 @@
       </c>
       <c r="B34" s="8">
         <f>IF($B$10="Home",260000,IF($B$10="Office",350000,IF($B$10="Factory",300000,420000)))</f>
-        <v>420000</v>
+        <v>260000</v>
       </c>
       <c r="C34" s="31"/>
       <c r="E34" s="31" t="s">
@@ -8529,7 +9511,7 @@
       </c>
       <c r="B35" s="8">
         <f>IF($B$10="Home",230000,IF($B$10="Office",300000,IF($B$10="Factory",220000,380000)))</f>
-        <v>380000</v>
+        <v>230000</v>
       </c>
       <c r="C35" s="31"/>
       <c r="I35" t="s">
@@ -8560,7 +9542,7 @@
       </c>
       <c r="B36" s="6">
         <f>IF($B$10="Home",0.12,IF($B$10="Office",0.15,IF($B$10="Factory",0.12,0.2)))</f>
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="C36" s="31"/>
       <c r="I36" t="s">
@@ -8691,12 +9673,12 @@
       </c>
     </row>
     <row r="41" spans="1:18">
-      <c r="A41" s="118" t="s">
+      <c r="A41" s="132" t="s">
         <v>176</v>
       </c>
-      <c r="B41" s="119"/>
-      <c r="C41" s="119"/>
-      <c r="D41" s="119"/>
+      <c r="B41" s="131"/>
+      <c r="C41" s="131"/>
+      <c r="D41" s="131"/>
       <c r="F41" s="92" t="s">
         <v>1011</v>
       </c>
@@ -9126,7 +10108,7 @@
       </c>
       <c r="B59" s="53">
         <f>1-(B20/24)</f>
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="N59" t="s">
         <v>200</v>
@@ -9138,17 +10120,17 @@
       </c>
     </row>
     <row r="61" spans="1:18">
-      <c r="A61" s="126" t="s">
+      <c r="A61" s="119" t="s">
         <v>1025</v>
       </c>
-      <c r="B61" s="127" t="s">
+      <c r="B61" s="120" t="s">
         <v>1030</v>
       </c>
-      <c r="C61" s="125" t="s">
+      <c r="C61" s="118" t="s">
         <v>1026</v>
       </c>
-      <c r="D61" s="125"/>
-      <c r="E61" s="125"/>
+      <c r="D61" s="118"/>
+      <c r="E61" s="118"/>
       <c r="F61" t="s">
         <v>1029</v>
       </c>
@@ -9157,17 +10139,17 @@
       </c>
     </row>
     <row r="62" spans="1:18">
-      <c r="A62" s="126" t="s">
+      <c r="A62" s="119" t="s">
         <v>1027</v>
       </c>
       <c r="B62" s="7">
         <v>1200</v>
       </c>
-      <c r="C62" s="125" t="s">
+      <c r="C62" s="118" t="s">
         <v>1028</v>
       </c>
-      <c r="D62" s="125"/>
-      <c r="E62" s="125"/>
+      <c r="D62" s="118"/>
+      <c r="E62" s="118"/>
       <c r="N62" t="s">
         <v>210</v>
       </c>
@@ -9220,7 +10202,7 @@
       <formula1>"209.50, 63.00, 50.00, 43.00, 40.00"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B61" xr:uid="{E007E95E-EAFD-4F63-A920-B1F95CFC0394}">
-      <formula1>"0-2 hours,3-6 hours,7-12 hours,13-18 hours,19-24 hours"</formula1>
+      <formula1>"0-2 hours,2-6 hours,6-12 hours,12-18 hours,18-24 hours"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9243,16 +10225,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="24" customHeight="1">
-      <c r="A1" s="120"/>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
+      <c r="A1" s="130"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1"/>
@@ -9310,7 +10292,7 @@
     <row r="8" spans="1:4">
       <c r="B8" s="43" t="str">
         <f>User_Inputs!B10</f>
-        <v>Hotel</v>
+        <v>Home</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -9321,7 +10303,7 @@
     <row r="10" spans="1:4">
       <c r="B10" t="str">
         <f>User_Inputs!B8</f>
-        <v>Lagos</v>
+        <v>Akwa Ibom</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -9342,31 +10324,31 @@
     <row r="15" spans="1:4">
       <c r="B15" t="str">
         <f>Lead_Routing!B4</f>
-        <v>Medium</v>
+        <v>Small</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="B16" s="41">
         <f>Load_Estimation!B8/30</f>
-        <v>96.45</v>
+        <v>13.397499999999999</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17">
         <f>Outputs!B10</f>
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18">
         <f>Outputs!B11</f>
-        <v>120</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" s="39">
         <f>Outputs!B12</f>
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="2:2">
@@ -10637,7 +11619,7 @@
       </c>
       <c r="F5" s="102">
         <f>IF(C5="","",IFERROR(IF(VALUE(LEFT(Customer_Profile!$B$19,FIND("-",Customer_Profile!$B$19&amp;"-")-1))&lt;=Installer_Database!J5,15,IF(VALUE(LEFT(Customer_Profile!$B$19,FIND("-",Customer_Profile!$B$19&amp;"-")-1))&lt;=Installer_Database!J5*1.25,10,5)),8))</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G5" s="102">
         <f>IF(C5="","",IF(Installer_Database!V5="Excellent",15,IF(Installer_Database!V5="Good",12,IF(Installer_Database!V5="Acceptable",8,IF(Installer_Database!V5="Weak",4,IF(Installer_Database!V5="Unverified",5,5))))))</f>
@@ -10665,7 +11647,7 @@
       </c>
       <c r="M5" s="116">
         <f t="shared" ref="M5:M65" si="0">IF(C5="","",SUM(D5:L5))</f>
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="N5" s="116">
         <f>100</f>
@@ -10673,7 +11655,7 @@
       </c>
       <c r="O5" s="117">
         <f t="shared" ref="O5:O65" si="1">IF(C5="","",M5/N5)</f>
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="P5" s="102" t="str">
         <f t="shared" ref="P5:P65" si="2">IF(C5="","",IF(O5&gt;=0.85,"Excellent Match",IF(O5&gt;=0.7,"Good Match",IF(O5&gt;=0.55,"Possible Match","Do Not Recommend"))))</f>
@@ -10716,7 +11698,7 @@
       </c>
       <c r="E6" s="102">
         <f>IF(C6="","",IF(ISNUMBER(SEARCH(Customer_Profile!$B$8,Installer_Database!H6)),15,IF(OR(AND(Customer_Profile!$B$8="Hospital",ISNUMBER(SEARCH("Commercial",Installer_Database!H6))),AND(Customer_Profile!$B$8="Hotel",ISNUMBER(SEARCH("Commercial",Installer_Database!H6))),AND(Customer_Profile!$B$8="School",ISNUMBER(SEARCH("Commercial",Installer_Database!H6)))),8,0)))</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F6" s="102">
         <f>IF(C6="","",IFERROR(IF(VALUE(LEFT(Customer_Profile!$B$19,FIND("-",Customer_Profile!$B$19&amp;"-")-1))&lt;=Installer_Database!J6,15,IF(VALUE(LEFT(Customer_Profile!$B$19,FIND("-",Customer_Profile!$B$19&amp;"-")-1))&lt;=Installer_Database!J6*1.25,10,5)),8))</f>
@@ -10748,7 +11730,7 @@
       </c>
       <c r="M6" s="116">
         <f t="shared" si="0"/>
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="N6" s="116">
         <f>100</f>
@@ -10756,7 +11738,7 @@
       </c>
       <c r="O6" s="117">
         <f t="shared" si="1"/>
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="P6" s="102" t="str">
         <f t="shared" si="2"/>
@@ -10769,7 +11751,7 @@
       <c r="R6" s="102" t="str">
         <f t="shared" ref="R6:R69" si="4">IF(C6="","",IF(LEN(IF(D6&gt;=12,"; serves your location","") &amp;IF(E6&gt;=15,"; experienced in your project type",IF(E6&gt;=8,"; related project experience","")) &amp;IF(H6&gt;=7,"; good battery/hybrid capability","") &amp;IF(J6&gt;=8,"; strong after-sales support",""))=0,"",
 MID(IF(D6&gt;=12,"; serves your location","") &amp;IF(E6&gt;=15,"; experienced in your project type",IF(E6&gt;=8,"; related project experience","")) &amp;IF(H6&gt;=7,"; good battery/hybrid capability","") &amp;IF(J6&gt;=8,"; strong after-sales support",""),3,999)))</f>
-        <v>serves your location; related project experience; good battery/hybrid capability; strong after-sales support</v>
+        <v>serves your location; experienced in your project type; good battery/hybrid capability; strong after-sales support</v>
       </c>
       <c r="S6" s="102" t="str">
         <f>IF(C6="","",Installer_Database!Z6)</f>
@@ -10777,7 +11759,7 @@
       </c>
       <c r="T6" s="102">
         <f t="shared" ref="T6:T69" si="5">IFERROR(RANK(O6,$O$5:$O$104,0),"")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -10799,7 +11781,7 @@
       </c>
       <c r="E7" s="102">
         <f>IF(C7="","",IF(ISNUMBER(SEARCH(Customer_Profile!$B$8,Installer_Database!H7)),15,IF(OR(AND(Customer_Profile!$B$8="Hospital",ISNUMBER(SEARCH("Commercial",Installer_Database!H7))),AND(Customer_Profile!$B$8="Hotel",ISNUMBER(SEARCH("Commercial",Installer_Database!H7))),AND(Customer_Profile!$B$8="School",ISNUMBER(SEARCH("Commercial",Installer_Database!H7)))),8,0)))</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F7" s="102">
         <f>IF(C7="","",IFERROR(IF(VALUE(LEFT(Customer_Profile!$B$19,FIND("-",Customer_Profile!$B$19&amp;"-")-1))&lt;=Installer_Database!J7,15,IF(VALUE(LEFT(Customer_Profile!$B$19,FIND("-",Customer_Profile!$B$19&amp;"-")-1))&lt;=Installer_Database!J7*1.25,10,5)),8))</f>
@@ -10831,7 +11813,7 @@
       </c>
       <c r="M7" s="116">
         <f t="shared" si="0"/>
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="N7" s="116">
         <f>100</f>
@@ -10839,7 +11821,7 @@
       </c>
       <c r="O7" s="117">
         <f t="shared" si="1"/>
-        <v>0.81</v>
+        <v>0.73</v>
       </c>
       <c r="P7" s="102" t="str">
         <f t="shared" si="2"/>
@@ -10851,7 +11833,7 @@
       </c>
       <c r="R7" s="102" t="str">
         <f t="shared" si="4"/>
-        <v>serves your location; related project experience; good battery/hybrid capability; strong after-sales support</v>
+        <v>serves your location; good battery/hybrid capability; strong after-sales support</v>
       </c>
       <c r="S7" s="102" t="str">
         <f>IF(C7="","",Installer_Database!Z7)</f>
@@ -10941,7 +11923,7 @@
       </c>
       <c r="T8" s="102">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -10963,11 +11945,11 @@
       </c>
       <c r="E9" s="102">
         <f>IF(C9="","",IF(ISNUMBER(SEARCH(Customer_Profile!$B$8,Installer_Database!H9)),15,IF(OR(AND(Customer_Profile!$B$8="Hospital",ISNUMBER(SEARCH("Commercial",Installer_Database!H9))),AND(Customer_Profile!$B$8="Hotel",ISNUMBER(SEARCH("Commercial",Installer_Database!H9))),AND(Customer_Profile!$B$8="School",ISNUMBER(SEARCH("Commercial",Installer_Database!H9)))),8,0)))</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F9" s="102">
         <f>IF(C9="","",IFERROR(IF(VALUE(LEFT(Customer_Profile!$B$19,FIND("-",Customer_Profile!$B$19&amp;"-")-1))&lt;=Installer_Database!J9,15,IF(VALUE(LEFT(Customer_Profile!$B$19,FIND("-",Customer_Profile!$B$19&amp;"-")-1))&lt;=Installer_Database!J9*1.25,10,5)),8))</f>
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G9" s="102">
         <f>IF(C9="","",IF(Installer_Database!V9="Excellent",15,IF(Installer_Database!V9="Good",12,IF(Installer_Database!V9="Acceptable",8,IF(Installer_Database!V9="Weak",4,IF(Installer_Database!V9="Unverified",5,5))))))</f>
@@ -10995,7 +11977,7 @@
       </c>
       <c r="M9" s="116">
         <f t="shared" si="0"/>
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="N9" s="116">
         <f>100</f>
@@ -11003,19 +11985,19 @@
       </c>
       <c r="O9" s="117">
         <f t="shared" si="1"/>
-        <v>0.55000000000000004</v>
+        <v>0.72</v>
       </c>
       <c r="P9" s="102" t="str">
         <f t="shared" si="2"/>
-        <v>Possible Match</v>
+        <v>Good Match</v>
       </c>
       <c r="Q9" s="102" t="str">
         <f t="shared" si="3"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R9" s="102" t="str">
         <f t="shared" si="4"/>
-        <v>serves your location; related project experience</v>
+        <v>serves your location; experienced in your project type</v>
       </c>
       <c r="S9" s="102" t="str">
         <f>IF(C9="","",Installer_Database!Z9)</f>
@@ -11045,7 +12027,7 @@
       </c>
       <c r="E10" s="102">
         <f>IF(C10="","",IF(ISNUMBER(SEARCH(Customer_Profile!$B$8,Installer_Database!H10)),15,IF(OR(AND(Customer_Profile!$B$8="Hospital",ISNUMBER(SEARCH("Commercial",Installer_Database!H10))),AND(Customer_Profile!$B$8="Hotel",ISNUMBER(SEARCH("Commercial",Installer_Database!H10))),AND(Customer_Profile!$B$8="School",ISNUMBER(SEARCH("Commercial",Installer_Database!H10)))),8,0)))</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F10" s="102">
         <f>IF(C10="","",IFERROR(IF(VALUE(LEFT(Customer_Profile!$B$19,FIND("-",Customer_Profile!$B$19&amp;"-")-1))&lt;=Installer_Database!J10,15,IF(VALUE(LEFT(Customer_Profile!$B$19,FIND("-",Customer_Profile!$B$19&amp;"-")-1))&lt;=Installer_Database!J10*1.25,10,5)),8))</f>
@@ -11077,7 +12059,7 @@
       </c>
       <c r="M10" s="116">
         <f t="shared" si="0"/>
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="N10" s="116">
         <f>100</f>
@@ -11085,11 +12067,11 @@
       </c>
       <c r="O10" s="117">
         <f t="shared" si="1"/>
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="P10" s="102" t="str">
         <f t="shared" si="2"/>
-        <v>Excellent Match</v>
+        <v>Good Match</v>
       </c>
       <c r="Q10" s="102" t="str">
         <f t="shared" si="3"/>
@@ -11097,7 +12079,7 @@
       </c>
       <c r="R10" s="102" t="str">
         <f t="shared" si="4"/>
-        <v>serves your location; related project experience; good battery/hybrid capability; strong after-sales support</v>
+        <v>serves your location; good battery/hybrid capability; strong after-sales support</v>
       </c>
       <c r="S10" s="102" t="str">
         <f>IF(C10="","",Installer_Database!Z10)</f>
@@ -11105,7 +12087,7 @@
       </c>
       <c r="T10" s="102">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -18912,11 +19894,11 @@
       </c>
       <c r="B8" t="str">
         <f>Customer_Profile!B8</f>
-        <v>Hotel</v>
+        <v>Home</v>
       </c>
       <c r="C8" t="str">
         <f>Customer_Profile!B8</f>
-        <v>Hotel</v>
+        <v>Home</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -18925,11 +19907,11 @@
       </c>
       <c r="B9" s="41" t="str">
         <f>TEXT(Customer_Profile!B16,"0.0") &amp; " kWh/day"</f>
-        <v>96.5 kWh/day</v>
+        <v>13.4 kWh/day</v>
       </c>
       <c r="C9" s="41" t="str">
         <f>TEXT(Customer_Profile!B16,"0.0") &amp; " kWh/day"</f>
-        <v>96.5 kWh/day</v>
+        <v>13.4 kWh/day</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -18938,11 +19920,11 @@
       </c>
       <c r="B10" s="41" t="str">
         <f>TEXT(Customer_Profile!B17,"0.0") &amp; " kWp"</f>
-        <v>29.0 kWp</v>
+        <v>4.0 kWp</v>
       </c>
       <c r="C10" s="41" t="str">
         <f>TEXT(Customer_Profile!B17,"0.0") &amp; " kWp"</f>
-        <v>29.0 kWp</v>
+        <v>4.0 kWp</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -18951,11 +19933,11 @@
       </c>
       <c r="B11" s="41" t="str">
         <f>TEXT(Customer_Profile!B18,"0.0") &amp; " kWh"</f>
-        <v>120.0 kWh</v>
+        <v>15.0 kWh</v>
       </c>
       <c r="C11" s="41" t="str">
         <f>TEXT(Customer_Profile!B18,"0.0") &amp; " kWh"</f>
-        <v>120.0 kWh</v>
+        <v>15.0 kWh</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -18964,11 +19946,11 @@
       </c>
       <c r="B12" s="41" t="str">
         <f>TEXT(Customer_Profile!B19,"0.0") &amp; " kVA"</f>
-        <v>25.0 kVA</v>
+        <v>5.0 kVA</v>
       </c>
       <c r="C12" s="41" t="str">
         <f>TEXT(Customer_Profile!B19,"0.0") &amp; " kVA"</f>
-        <v>25.0 kVA</v>
+        <v>5.0 kVA</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -19016,7 +19998,7 @@
       </c>
       <c r="C16" s="27">
         <f>IF(B16="","",INDEX(Match_Engine!$O$5:$O$104,MATCH(B16,Match_Engine!$C$5:$C$104,0)))</f>
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="D16" t="str">
         <f>IF(B16="","",INDEX(Match_Engine!$P$5:$P$104,MATCH(B16,Match_Engine!$C$5:$C$104,0)))</f>
@@ -19024,7 +20006,7 @@
       </c>
       <c r="E16" t="str">
         <f>IF(B16="","",Customer_Profile!$B$8&amp;" projects")</f>
-        <v>Hotel projects</v>
+        <v>Home projects</v>
       </c>
       <c r="F16" t="str">
         <f>IF(B16="","",INDEX(Installer_Database!$F$5:$F$104,MATCH(B16,Installer_Database!$B$5:$B$104,0)))</f>
@@ -19055,11 +20037,11 @@
       </c>
       <c r="B17" t="str">
         <f>IFERROR(INDEX(Match_Engine!$C$5:$C$104,MATCH(LARGE(Match_Engine!$O$5:$O$104,2),Match_Engine!$O$5:$O$104,0)),"")</f>
-        <v>Lagos Hybrid Power Ltd</v>
+        <v>Abuja SolarCare Engineering</v>
       </c>
       <c r="C17" s="27">
         <f>IF(B17="","",INDEX(Match_Engine!$O$5:$O$104,MATCH(B17,Match_Engine!$C$5:$C$104,0)))</f>
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="D17" t="str">
         <f>IF(B17="","",INDEX(Match_Engine!$P$5:$P$104,MATCH(B17,Match_Engine!$C$5:$C$104,0)))</f>
@@ -19067,11 +20049,11 @@
       </c>
       <c r="E17" t="str">
         <f>IF(B17="","",Customer_Profile!$B$8&amp;" projects")</f>
-        <v>Hotel projects</v>
+        <v>Home projects</v>
       </c>
       <c r="F17" t="str">
         <f>IF(B17="","",INDEX(Installer_Database!$F$5:$F$104,MATCH(B17,Installer_Database!$B$5:$B$104,0)))</f>
-        <v>Lagos</v>
+        <v>Abuja FCT</v>
       </c>
       <c r="G17" t="str">
         <f>IF(B17="","",INDEX(Match_Engine!$R$5:$R$104,MATCH(B17,Match_Engine!$C$5:$C$104,0)))</f>
@@ -19079,11 +20061,11 @@
       </c>
       <c r="H17" t="str">
         <f>IF(B17="","",INDEX(Installer_Database!$U$5:$U$104,MATCH(B17,Installer_Database!$B$5:$B$104,0)))</f>
-        <v>Mid-range</v>
+        <v>Premium</v>
       </c>
       <c r="I17" t="str">
         <f>IF(B17="","",INDEX(Installer_Database!$T$5:$T$104,MATCH(B17,Installer_Database!$B$5:$B$104,0)))</f>
-        <v>Same day</v>
+        <v>24-48 hours</v>
       </c>
       <c r="J17" t="s">
         <v>816</v>
@@ -19098,11 +20080,11 @@
       </c>
       <c r="B18" t="str">
         <f>IFERROR(INDEX(Match_Engine!$C$5:$C$104,MATCH(LARGE(Match_Engine!$O$5:$O$104,3),Match_Engine!$O$5:$O$104,0)),"")</f>
-        <v>Prime Critical Power Systems</v>
+        <v>Rivers Reliable Solar</v>
       </c>
       <c r="C18" s="27">
         <f>IF(B18="","",INDEX(Match_Engine!$O$5:$O$104,MATCH(B18,Match_Engine!$C$5:$C$104,0)))</f>
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="D18" t="str">
         <f>IF(B18="","",INDEX(Match_Engine!$P$5:$P$104,MATCH(B18,Match_Engine!$C$5:$C$104,0)))</f>
@@ -19110,19 +20092,19 @@
       </c>
       <c r="E18" t="str">
         <f>IF(B18="","",Customer_Profile!$B$8&amp;" projects")</f>
-        <v>Hotel projects</v>
+        <v>Home projects</v>
       </c>
       <c r="F18" t="str">
         <f>IF(B18="","",INDEX(Installer_Database!$F$5:$F$104,MATCH(B18,Installer_Database!$B$5:$B$104,0)))</f>
-        <v>Abuja FCT; Kano; Kaduna</v>
+        <v>Rivers; Akwa Ibom</v>
       </c>
       <c r="G18" t="str">
         <f>IF(B18="","",INDEX(Match_Engine!$R$5:$R$104,MATCH(B18,Match_Engine!$C$5:$C$104,0)))</f>
-        <v>serves your location; related project experience; good battery/hybrid capability; strong after-sales support</v>
+        <v>serves your location; experienced in your project type; good battery/hybrid capability; strong after-sales support</v>
       </c>
       <c r="H18" t="str">
         <f>IF(B18="","",INDEX(Installer_Database!$U$5:$U$104,MATCH(B18,Installer_Database!$B$5:$B$104,0)))</f>
-        <v>Premium</v>
+        <v>Mid-range</v>
       </c>
       <c r="I18" t="str">
         <f>IF(B18="","",INDEX(Installer_Database!$T$5:$T$104,MATCH(B18,Installer_Database!$B$5:$B$104,0)))</f>
@@ -20123,16 +21105,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="130" t="s">
         <v>1000</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="79" t="s">
@@ -20164,7 +21146,7 @@
       </c>
       <c r="B7" s="21" t="str">
         <f>User_Inputs!B10</f>
-        <v>Hotel</v>
+        <v>Home</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -20192,7 +21174,7 @@
       </c>
       <c r="B11" s="64">
         <f>IF(User_Inputs!B15="Appliances", B44,IF(User_Inputs!B15="Bill", B39,IF(User_Inputs!B15="Custom", B49, "")))</f>
-        <v>2893.5</v>
+        <v>401.92499999999995</v>
       </c>
       <c r="C11" t="s">
         <v>561</v>
@@ -20204,7 +21186,7 @@
       </c>
       <c r="B12" s="60">
         <f>Load_Estimation!B9</f>
-        <v>34722</v>
+        <v>4823.0999999999995</v>
       </c>
       <c r="C12" t="s">
         <v>561</v>
@@ -20216,7 +21198,7 @@
       </c>
       <c r="B13" s="22">
         <f>B20</f>
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C13" t="s">
         <v>563</v>
@@ -20259,7 +21241,7 @@
       </c>
       <c r="B18" s="22">
         <f>Solar_Sizing!B12</f>
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="C18" t="s">
         <v>559</v>
@@ -20271,7 +21253,7 @@
       </c>
       <c r="B19" s="22">
         <f>Battery_Sizing!B10</f>
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
         <v>561</v>
@@ -20283,7 +21265,7 @@
       </c>
       <c r="B20" s="22">
         <f>Battery_Sizing!B12</f>
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C20" t="s">
         <v>563</v>
@@ -20295,7 +21277,7 @@
       </c>
       <c r="B21" s="23">
         <f>Solar_Sizing!B13</f>
-        <v>42050</v>
+        <v>5800</v>
       </c>
       <c r="C21" t="s">
         <v>561</v>
@@ -20307,7 +21289,7 @@
       </c>
       <c r="B22" s="23">
         <f>Solar_Sizing!B14</f>
-        <v>31537.5</v>
+        <v>4350</v>
       </c>
       <c r="C22" s="88" t="s">
         <v>561</v>
@@ -20329,7 +21311,7 @@
       </c>
       <c r="B25" s="24">
         <f>Financial_Model!B9</f>
-        <v>91020000</v>
+        <v>7000000</v>
       </c>
       <c r="C25" t="s">
         <v>534</v>
@@ -20341,7 +21323,7 @@
       </c>
       <c r="B26" s="24">
         <f>Financial_Model!B10</f>
-        <v>6607106.25</v>
+        <v>1072123.7089285715</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -20350,7 +21332,7 @@
       </c>
       <c r="B27" s="24">
         <f>Financial_Model!B11</f>
-        <v>1820400</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -20359,7 +21341,7 @@
       </c>
       <c r="B28" s="24">
         <f>Financial_Model!B12</f>
-        <v>4786706.25</v>
+        <v>932123.70892857155</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -20368,7 +21350,7 @@
       </c>
       <c r="B29" s="25">
         <f>Financial_Model!B13</f>
-        <v>19.015163088397163</v>
+        <v>7.5097328100860574</v>
       </c>
       <c r="C29" t="s">
         <v>568</v>
@@ -20389,7 +21371,7 @@
       </c>
       <c r="B32" s="54">
         <f>IFERROR(Solar_Sizing!B14/Load_Estimation!B9,0)</f>
-        <v>0.90828581302920341</v>
+        <v>0.90190956024133861</v>
       </c>
       <c r="C32" t="s">
         <v>939</v>
@@ -20401,7 +21383,7 @@
       </c>
       <c r="B33" s="54">
         <f>IFERROR(Diesel_Economics!B24/Diesel_Economics!B12,0)</f>
-        <v>0.90828581302920341</v>
+        <v>0.86921274698845152</v>
       </c>
       <c r="C33" t="s">
         <v>940</v>
@@ -20413,7 +21395,7 @@
       </c>
       <c r="B34" s="54">
         <f>IFERROR(Diesel_Economics!B8/Diesel_Economics!B11,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C34" t="s">
         <v>941</v>
@@ -20430,7 +21412,7 @@
       </c>
       <c r="B38" s="60">
         <f>Load_Estimation!B9</f>
-        <v>34722</v>
+        <v>4823.0999999999995</v>
       </c>
       <c r="C38" t="s">
         <v>561</v>
@@ -20468,7 +21450,7 @@
       </c>
       <c r="B43" s="63">
         <f>Appliance_Input!L4</f>
-        <v>96.45</v>
+        <v>13.397500000000003</v>
       </c>
       <c r="C43" t="s">
         <v>561</v>
@@ -20480,7 +21462,7 @@
       </c>
       <c r="B44" s="64">
         <f>Appliance_Input!L5</f>
-        <v>2893.5</v>
+        <v>401.92499999999995</v>
       </c>
       <c r="C44" t="s">
         <v>561</v>
@@ -20492,7 +21474,7 @@
       </c>
       <c r="B45" s="60">
         <f>Load_Estimation!B9</f>
-        <v>34722</v>
+        <v>4823.0999999999995</v>
       </c>
       <c r="C45" t="s">
         <v>561</v>
@@ -20533,7 +21515,7 @@
       </c>
       <c r="B50" s="60">
         <f>Load_Estimation!B9</f>
-        <v>34722</v>
+        <v>4823.0999999999995</v>
       </c>
       <c r="C50" t="s">
         <v>561</v>
@@ -20550,7 +21532,7 @@
       </c>
       <c r="B53" s="22">
         <f>Financial_Model!B16</f>
-        <v>138.73152884228384</v>
+        <v>86.682221131907681</v>
       </c>
       <c r="C53" s="88" t="s">
         <v>1002</v>
@@ -20584,6 +21566,520 @@
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{081EC080-D680-4E77-BCF5-8807726720D1}">
+  <sheetPr>
+    <tabColor rgb="FF0070C0"/>
+  </sheetPr>
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="33.36328125" customWidth="1"/>
+    <col min="2" max="2" width="28.26953125" customWidth="1"/>
+    <col min="3" max="3" width="66.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.5">
+      <c r="A1" s="121" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="122" t="s">
+        <v>222</v>
+      </c>
+      <c r="B3" s="122" t="s">
+        <v>223</v>
+      </c>
+      <c r="C3" s="122" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="127" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B4" s="123">
+        <f>Outputs!B15</f>
+        <v>7000000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="127" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B5" s="123">
+        <f>Outputs!B10</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="127" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B6" s="123">
+        <f>Outputs!B11</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="127" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B7" s="123">
+        <f>Outputs!B18</f>
+        <v>932123.70892857155</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="127" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B8" s="123">
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="127" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B9" s="124">
+        <f>MAX(0,B4-B8)</f>
+        <v>4500000</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B10" s="125">
+        <f>IFERROR(B8/B4,0)</f>
+        <v>0.35714285714285715</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="127" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B11" s="126" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="127" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B12" s="126" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C12">
+        <f>LOOKUP(B12,{"12-24 months","24-36 months","36+ months"},{12,24,36})</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="127" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B13" s="126" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>819</v>
+      </c>
+      <c r="B14" s="126" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="127" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B15" s="123" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="127" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B16" s="126" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B17" t="str">
+        <f>IF(AND(B4&gt;0,B8&gt;=0,B8&lt;=B4,B12&gt;0),"VALID","CHECK INPUTS")</f>
+        <v>VALID</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="C18" s="30"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="C19" s="30"/>
+    </row>
+  </sheetData>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="B11" xr:uid="{E946082D-6CDC-4EFA-9EBA-B6504D3C103B}">
+      <formula1>"Any,Asset financing,Solar instalment plan,Energy-as-a-Service / lease"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="B16" xr:uid="{419E1517-2D80-47B3-B349-36FBC323A83A}">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="B13" xr:uid="{17F407BE-F973-400E-AB73-2B2610B0C446}">
+      <formula1>"Individual / Homeowner,SME,Corporate"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12" xr:uid="{15C5F2EF-4232-4C35-A195-50A1C91A2C54}">
+      <formula1>"12-24 months,24-36 months,36+ months"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15" xr:uid="{5FF33253-ECDA-401B-8F50-93FEB91D6CD9}">
+      <formula1>"Below 500k,500k-1m,1m-5m,Above 5m"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC45912-4999-4BF0-9A27-8F8BA4655590}">
+  <sheetPr>
+    <tabColor rgb="FF0070C0"/>
+  </sheetPr>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="13.26953125" customWidth="1"/>
+    <col min="2" max="2" width="42.1796875" customWidth="1"/>
+    <col min="3" max="3" width="30.08984375" customWidth="1"/>
+    <col min="4" max="4" width="28.08984375" customWidth="1"/>
+    <col min="5" max="5" width="25.7265625" customWidth="1"/>
+    <col min="6" max="6" width="21" customWidth="1"/>
+    <col min="7" max="7" width="54.54296875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="128" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B1" s="128" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C1" s="128" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D1" s="128" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E1" s="128" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F1" s="128" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G1" s="128" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1057</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="33" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -20604,25 +22100,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="130" t="s">
         <v>220</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="132" t="s">
         <v>221</v>
       </c>
-      <c r="B3" s="119"/>
-      <c r="C3" s="119"/>
-      <c r="D3" s="119"/>
-      <c r="E3" s="119"/>
+      <c r="B3" s="131"/>
+      <c r="C3" s="131"/>
+      <c r="D3" s="131"/>
+      <c r="E3" s="131"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="13" t="s">
@@ -20754,6 +22250,1575 @@
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3B01BB-40D0-4DE1-AAD5-4D4906E75543}">
+  <sheetPr>
+    <tabColor rgb="FF0070C0"/>
+  </sheetPr>
+  <dimension ref="A1:P13"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="14.90625" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" customWidth="1"/>
+    <col min="3" max="3" width="30.54296875" customWidth="1"/>
+    <col min="4" max="4" width="28.36328125" customWidth="1"/>
+    <col min="5" max="5" width="24.08984375" customWidth="1"/>
+    <col min="6" max="6" width="23.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.7265625" customWidth="1"/>
+    <col min="8" max="8" width="13.90625" customWidth="1"/>
+    <col min="9" max="9" width="14.7265625" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" customWidth="1"/>
+    <col min="12" max="12" width="18.6328125" customWidth="1"/>
+    <col min="13" max="13" width="15.6328125" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="91.453125" customWidth="1"/>
+    <col min="16" max="16" width="17" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="28.5" customHeight="1">
+      <c r="A1" s="128" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B1" s="128" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C1" s="128" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D1" s="128" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E1" s="128" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F1" s="128" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G1" s="128" t="s">
+        <v>1100</v>
+      </c>
+      <c r="H1" s="128" t="s">
+        <v>1101</v>
+      </c>
+      <c r="I1" s="128" t="s">
+        <v>1102</v>
+      </c>
+      <c r="J1" s="128" t="s">
+        <v>1103</v>
+      </c>
+      <c r="K1" s="128" t="s">
+        <v>1104</v>
+      </c>
+      <c r="L1" s="128" t="s">
+        <v>1105</v>
+      </c>
+      <c r="M1" s="128" t="s">
+        <v>1106</v>
+      </c>
+      <c r="N1" s="128" t="s">
+        <v>1107</v>
+      </c>
+      <c r="O1" s="128" t="s">
+        <v>1108</v>
+      </c>
+      <c r="P1" s="128" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G2" s="124">
+        <v>25000</v>
+      </c>
+      <c r="H2" s="124">
+        <v>120000000</v>
+      </c>
+      <c r="I2" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="J2">
+        <v>12</v>
+      </c>
+      <c r="K2">
+        <v>60</v>
+      </c>
+      <c r="L2" s="125">
+        <v>0.2</v>
+      </c>
+      <c r="M2" s="124">
+        <v>25000</v>
+      </c>
+      <c r="N2" s="124">
+        <v>500</v>
+      </c>
+      <c r="O2" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E3" t="s">
+        <v>387</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G3" s="124">
+        <v>5000</v>
+      </c>
+      <c r="H3" s="124">
+        <v>120000000</v>
+      </c>
+      <c r="I3" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="J3">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>72</v>
+      </c>
+      <c r="L3" s="125">
+        <v>0.22</v>
+      </c>
+      <c r="M3" s="124">
+        <v>30000</v>
+      </c>
+      <c r="N3" s="124">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G4" s="124">
+        <v>25000</v>
+      </c>
+      <c r="H4" s="124">
+        <v>130000000</v>
+      </c>
+      <c r="I4" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="J4">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <v>60</v>
+      </c>
+      <c r="L4" s="125"/>
+      <c r="M4" s="124">
+        <v>35000</v>
+      </c>
+      <c r="N4" s="124">
+        <v>500</v>
+      </c>
+      <c r="O4" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G5" s="124">
+        <v>50000</v>
+      </c>
+      <c r="H5" s="124">
+        <v>120000000</v>
+      </c>
+      <c r="I5" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="J5">
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <v>72</v>
+      </c>
+      <c r="L5" s="125">
+        <v>0.26</v>
+      </c>
+      <c r="M5" s="124">
+        <v>40000</v>
+      </c>
+      <c r="N5" s="124">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1115</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E6" t="s">
+        <v>387</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G6" s="124">
+        <v>25000</v>
+      </c>
+      <c r="H6" s="124">
+        <v>120000000</v>
+      </c>
+      <c r="I6" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="J6">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>60</v>
+      </c>
+      <c r="L6" s="125">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M6" s="124">
+        <v>45000</v>
+      </c>
+      <c r="N6" s="124">
+        <v>500</v>
+      </c>
+      <c r="O6" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1117</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G7" s="124">
+        <v>50000</v>
+      </c>
+      <c r="H7" s="124">
+        <v>130000000</v>
+      </c>
+      <c r="I7" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="J7">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>72</v>
+      </c>
+      <c r="L7" s="125">
+        <v>0.18</v>
+      </c>
+      <c r="M7" s="124">
+        <v>50000</v>
+      </c>
+      <c r="N7" s="124">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G8" s="124">
+        <v>25000</v>
+      </c>
+      <c r="H8" s="124">
+        <v>120000000</v>
+      </c>
+      <c r="I8" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="J8">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <v>60</v>
+      </c>
+      <c r="L8" s="125">
+        <v>0.2</v>
+      </c>
+      <c r="M8" s="124">
+        <v>55000</v>
+      </c>
+      <c r="N8" s="124">
+        <v>500</v>
+      </c>
+      <c r="O8" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E9" t="s">
+        <v>387</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G9" s="124">
+        <v>50000</v>
+      </c>
+      <c r="H9" s="124">
+        <v>120000000</v>
+      </c>
+      <c r="I9" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="J9">
+        <v>12</v>
+      </c>
+      <c r="K9">
+        <v>72</v>
+      </c>
+      <c r="L9" s="125"/>
+      <c r="M9" s="124">
+        <v>60000</v>
+      </c>
+      <c r="N9" s="124">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1067</v>
+      </c>
+      <c r="G10" s="124">
+        <v>25000</v>
+      </c>
+      <c r="H10" s="124">
+        <v>130000000</v>
+      </c>
+      <c r="I10" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="J10">
+        <v>12</v>
+      </c>
+      <c r="K10">
+        <v>60</v>
+      </c>
+      <c r="L10" s="125">
+        <v>0.24</v>
+      </c>
+      <c r="M10" s="124">
+        <v>65000</v>
+      </c>
+      <c r="N10" s="124">
+        <v>500</v>
+      </c>
+      <c r="O10" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G11" s="124">
+        <v>50000</v>
+      </c>
+      <c r="H11" s="124">
+        <v>120000000</v>
+      </c>
+      <c r="I11" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="J11">
+        <v>12</v>
+      </c>
+      <c r="K11">
+        <v>72</v>
+      </c>
+      <c r="L11" s="125">
+        <v>0.26</v>
+      </c>
+      <c r="M11" s="124">
+        <v>70000</v>
+      </c>
+      <c r="N11" s="124">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1122</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E12" t="s">
+        <v>387</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G12" s="124">
+        <v>25000</v>
+      </c>
+      <c r="H12" s="124">
+        <v>120000000</v>
+      </c>
+      <c r="I12" s="27">
+        <v>0.1</v>
+      </c>
+      <c r="J12">
+        <v>12</v>
+      </c>
+      <c r="K12">
+        <v>60</v>
+      </c>
+      <c r="L12" s="125">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M12" s="124">
+        <v>75000</v>
+      </c>
+      <c r="N12" s="124">
+        <v>500</v>
+      </c>
+      <c r="O12" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1062</v>
+      </c>
+      <c r="G13" s="124">
+        <v>50000</v>
+      </c>
+      <c r="H13" s="124">
+        <v>130000000</v>
+      </c>
+      <c r="I13" s="27">
+        <v>0.2</v>
+      </c>
+      <c r="J13">
+        <v>12</v>
+      </c>
+      <c r="K13">
+        <v>72</v>
+      </c>
+      <c r="L13" s="125"/>
+      <c r="M13" s="124">
+        <v>80000</v>
+      </c>
+      <c r="N13" s="124">
+        <v>0</v>
+      </c>
+      <c r="O13" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="33" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F38CF07-43FB-475F-9B65-E82CED7E6329}">
+  <sheetPr>
+    <tabColor rgb="FF92D050"/>
+  </sheetPr>
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="37.453125" customWidth="1"/>
+    <col min="3" max="3" width="27.7265625" customWidth="1"/>
+    <col min="4" max="4" width="11.54296875" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.453125" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="10.90625" customWidth="1"/>
+    <col min="9" max="9" width="10.1796875" customWidth="1"/>
+    <col min="10" max="10" width="21.90625" customWidth="1"/>
+    <col min="11" max="11" width="21.81640625" customWidth="1"/>
+    <col min="12" max="12" width="18.81640625" customWidth="1"/>
+    <col min="13" max="13" width="15.90625" customWidth="1"/>
+    <col min="14" max="14" width="93.6328125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="28.5" customHeight="1">
+      <c r="A1" s="128" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B1" s="128" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C1" s="128" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D1" s="128" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E1" s="128" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F1" s="128" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G1" s="128" t="s">
+        <v>1133</v>
+      </c>
+      <c r="H1" s="128" t="s">
+        <v>1134</v>
+      </c>
+      <c r="I1" s="128" t="s">
+        <v>1135</v>
+      </c>
+      <c r="J1" s="128" t="s">
+        <v>1136</v>
+      </c>
+      <c r="K1" s="128" t="s">
+        <v>1137</v>
+      </c>
+      <c r="L1" s="128" t="s">
+        <v>1138</v>
+      </c>
+      <c r="M1" s="128" t="s">
+        <v>1106</v>
+      </c>
+      <c r="N1" s="128" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="str">
+        <f>Finance_Products!A2</f>
+        <v>F001</v>
+      </c>
+      <c r="B2" t="str">
+        <f>IFERROR(INDEX(Finance_Partners!$B$2:$B$13,MATCH(Finance_Products!B2,Finance_Partners!$A$2:$A$13,0)),"")</f>
+        <v>SunBridge Capital</v>
+      </c>
+      <c r="C2" t="str">
+        <f>Finance_Products!D2</f>
+        <v>Asset financing</v>
+      </c>
+      <c r="D2" t="str">
+        <f>IF(AND(Finance_Request!$B$9&gt;=Finance_Products!G2,Finance_Request!$B$9&lt;=Finance_Products!H2),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="E2" t="str">
+        <f>IF(Finance_Request!$B$10&gt;=Finance_Products!I2,"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="F2" t="str">
+        <f>IF(AND(Finance_Request!$C$12&gt;=Finance_Products!J2,Finance_Request!$C$12&lt;=Finance_Products!K2),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="G2" t="str">
+        <f>IF(OR(Finance_Products!E2="All",Finance_Products!E2=Finance_Request!$B$13),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="H2" t="str">
+        <f>IF(OR(Finance_Products!F2="All",ISNUMBER(SEARCH(","&amp;LOWER(Finance_Request!$B$14)&amp;",",","&amp;LOWER(SUBSTITUTE(Finance_Products!F2,", ",","))&amp;","))),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="I2" t="str">
+        <f>IF(OR(Finance_Request!$B$11="Any",Finance_Request!$B$11=Finance_Products!D2),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="J2" t="str">
+        <f>IF(AND(D2="YES",E2="YES",F2="YES",G2="YES",H2="YES",I2="YES",Finance_Request!$B$17="VALID"),"PRELIMINARY MATCH","NOT MATCHED")</f>
+        <v>PRELIMINARY MATCH</v>
+      </c>
+      <c r="K2" s="129">
+        <f>IF(AND(J2="PRELIMINARY MATCH",ISNUMBER([1]Finance_Products!L2),[1]Finance_Products!D2&lt;&gt;"Energy-as-a-Service / lease"),IF([1]Finance_Products!L2=0,[1]Customer_Scenario!$B$8/[1]Customer_Scenario!$B$11,-PMT([1]Finance_Products!L2/12,[1]Customer_Scenario!$B$11,[1]Customer_Scenario!$B$8))+[1]Finance_Products!N2,"")</f>
+        <v>256185.45351501429</v>
+      </c>
+      <c r="L2" s="129">
+        <f>IF(ISNUMBER(K2),K2*[1]Customer_Scenario!$B$11+[1]Finance_Products!M2,"")</f>
+        <v>9247676.3265405148</v>
+      </c>
+      <c r="M2" s="129">
+        <f>[1]Finance_Products!M2</f>
+        <v>25000</v>
+      </c>
+      <c r="N2" t="str">
+        <f>Finance_Products!O2</f>
+        <v>ID, proof of address, income evidence, credit review and signed agreement</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="str">
+        <f>Finance_Products!A3</f>
+        <v>F002</v>
+      </c>
+      <c r="B3" t="str">
+        <f>IFERROR(INDEX(Finance_Partners!$B$2:$B$13,MATCH(Finance_Products!B3,Finance_Partners!$A$2:$A$13,0)),"")</f>
+        <v>Helio Credit</v>
+      </c>
+      <c r="C3" t="str">
+        <f>Finance_Products!D3</f>
+        <v>Asset financing</v>
+      </c>
+      <c r="D3" t="str">
+        <f>IF(AND(Finance_Request!$B$9&gt;=Finance_Products!G3,Finance_Request!$B$9&lt;=Finance_Products!H3),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="E3" t="str">
+        <f>IF(Finance_Request!$B$10&gt;=Finance_Products!I3,"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="F3" t="str">
+        <f>IF(AND(Finance_Request!$C$12&gt;=Finance_Products!J3,Finance_Request!$C$12&lt;=Finance_Products!K3),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="G3" t="str">
+        <f>IF(OR(Finance_Products!E3="All",Finance_Products!E3=Finance_Request!$B$13),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="H3" t="str">
+        <f>IF(OR(Finance_Products!F3="All",ISNUMBER(SEARCH(","&amp;LOWER(Finance_Request!$B$14)&amp;",",","&amp;LOWER(SUBSTITUTE(Finance_Products!F3,", ",","))&amp;","))),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="I3" t="str">
+        <f>IF(OR(Finance_Request!$B$11="Any",Finance_Request!$B$11=Finance_Products!D3),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="J3" t="str">
+        <f>IF(AND(D3="YES",E3="YES",F3="YES",G3="YES",H3="YES",I3="YES",Finance_Request!$B$17="VALID"),"PRELIMINARY MATCH","NOT MATCHED")</f>
+        <v>NOT MATCHED</v>
+      </c>
+      <c r="K3" s="129" t="str">
+        <f>IF(AND(J3="PRELIMINARY MATCH",ISNUMBER([1]Finance_Products!L3),[1]Finance_Products!D3&lt;&gt;"Energy-as-a-Service / lease"),IF([1]Finance_Products!L3=0,[1]Customer_Scenario!$B$8/[1]Customer_Scenario!$B$11,-PMT([1]Finance_Products!L3/12,[1]Customer_Scenario!$B$11,[1]Customer_Scenario!$B$8))+[1]Finance_Products!N3,"")</f>
+        <v/>
+      </c>
+      <c r="L3" s="129" t="str">
+        <f>IF(ISNUMBER(K3),K3*[1]Customer_Scenario!$B$11+[1]Finance_Products!M3,"")</f>
+        <v/>
+      </c>
+      <c r="M3" s="129">
+        <f>[1]Finance_Products!M3</f>
+        <v>30000</v>
+      </c>
+      <c r="N3" t="str">
+        <f>Finance_Products!O3</f>
+        <v>ID, proof of address, income evidence, credit review and signed agreement</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="str">
+        <f>Finance_Products!A4</f>
+        <v>F003</v>
+      </c>
+      <c r="B4" t="str">
+        <f>IFERROR(INDEX(Finance_Partners!$B$2:$B$13,MATCH(Finance_Products!B4,Finance_Partners!$A$2:$A$13,0)),"")</f>
+        <v>BrightLease Energy</v>
+      </c>
+      <c r="C4" t="str">
+        <f>Finance_Products!D4</f>
+        <v>Energy-as-a-Service / lease</v>
+      </c>
+      <c r="D4" t="str">
+        <f>IF(AND(Finance_Request!$B$9&gt;=Finance_Products!G4,Finance_Request!$B$9&lt;=Finance_Products!H4),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="E4" t="str">
+        <f>IF(Finance_Request!$B$10&gt;=Finance_Products!I4,"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="F4" t="str">
+        <f>IF(AND(Finance_Request!$C$12&gt;=Finance_Products!J4,Finance_Request!$C$12&lt;=Finance_Products!K4),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="G4" t="str">
+        <f>IF(OR(Finance_Products!E4="All",Finance_Products!E4=Finance_Request!$B$13),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="H4" t="str">
+        <f>IF(OR(Finance_Products!F4="All",ISNUMBER(SEARCH(","&amp;LOWER(Finance_Request!$B$14)&amp;",",","&amp;LOWER(SUBSTITUTE(Finance_Products!F4,", ",","))&amp;","))),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="I4" t="str">
+        <f>IF(OR(Finance_Request!$B$11="Any",Finance_Request!$B$11=Finance_Products!D4),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J4" t="str">
+        <f>IF(AND(D4="YES",E4="YES",F4="YES",G4="YES",H4="YES",I4="YES",Finance_Request!$B$17="VALID"),"PRELIMINARY MATCH","NOT MATCHED")</f>
+        <v>NOT MATCHED</v>
+      </c>
+      <c r="K4" s="129" t="str">
+        <f>IF(AND(J4="PRELIMINARY MATCH",ISNUMBER([1]Finance_Products!L4),[1]Finance_Products!D4&lt;&gt;"Energy-as-a-Service / lease"),IF([1]Finance_Products!L4=0,[1]Customer_Scenario!$B$8/[1]Customer_Scenario!$B$11,-PMT([1]Finance_Products!L4/12,[1]Customer_Scenario!$B$11,[1]Customer_Scenario!$B$8))+[1]Finance_Products!N4,"")</f>
+        <v/>
+      </c>
+      <c r="L4" s="129" t="str">
+        <f>IF(ISNUMBER(K4),K4*[1]Customer_Scenario!$B$11+[1]Finance_Products!M4,"")</f>
+        <v/>
+      </c>
+      <c r="M4" s="129">
+        <f>[1]Finance_Products!M4</f>
+        <v>35000</v>
+      </c>
+      <c r="N4" t="str">
+        <f>Finance_Products!O4</f>
+        <v>ID, address, income evidence, lender credit assessment, EaaS requires a separate usage-based quote</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="str">
+        <f>Finance_Products!A5</f>
+        <v>F004</v>
+      </c>
+      <c r="B5" t="str">
+        <f>IFERROR(INDEX(Finance_Partners!$B$2:$B$13,MATCH(Finance_Products!B5,Finance_Partners!$A$2:$A$13,0)),"")</f>
+        <v>GreenGrid Funding</v>
+      </c>
+      <c r="C5" t="str">
+        <f>Finance_Products!D5</f>
+        <v>Asset financing</v>
+      </c>
+      <c r="D5" t="str">
+        <f>IF(AND(Finance_Request!$B$9&gt;=Finance_Products!G5,Finance_Request!$B$9&lt;=Finance_Products!H5),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="E5" t="str">
+        <f>IF(Finance_Request!$B$10&gt;=Finance_Products!I5,"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="F5" t="str">
+        <f>IF(AND(Finance_Request!$C$12&gt;=Finance_Products!J5,Finance_Request!$C$12&lt;=Finance_Products!K5),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="G5" t="str">
+        <f>IF(OR(Finance_Products!E5="All",Finance_Products!E5=Finance_Request!$B$13),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="H5" t="str">
+        <f>IF(OR(Finance_Products!F5="All",ISNUMBER(SEARCH(","&amp;LOWER(Finance_Request!$B$14)&amp;",",","&amp;LOWER(SUBSTITUTE(Finance_Products!F5,", ",","))&amp;","))),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="I5" t="str">
+        <f>IF(OR(Finance_Request!$B$11="Any",Finance_Request!$B$11=Finance_Products!D5),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="J5" t="str">
+        <f>IF(AND(D5="YES",E5="YES",F5="YES",G5="YES",H5="YES",I5="YES",Finance_Request!$B$17="VALID"),"PRELIMINARY MATCH","NOT MATCHED")</f>
+        <v>PRELIMINARY MATCH</v>
+      </c>
+      <c r="K5" s="129">
+        <f>IF(AND(J5="PRELIMINARY MATCH",ISNUMBER([1]Finance_Products!L5),[1]Finance_Products!D5&lt;&gt;"Energy-as-a-Service / lease"),IF([1]Finance_Products!L5=0,[1]Customer_Scenario!$B$8/[1]Customer_Scenario!$B$11,-PMT([1]Finance_Products!L5/12,[1]Customer_Scenario!$B$11,[1]Customer_Scenario!$B$8))+[1]Finance_Products!N5,"")</f>
+        <v>277199.46935941442</v>
+      </c>
+      <c r="L5" s="129">
+        <f>IF(ISNUMBER(K5),K5*[1]Customer_Scenario!$B$11+[1]Finance_Products!M5,"")</f>
+        <v>10019180.89693892</v>
+      </c>
+      <c r="M5" s="129">
+        <f>[1]Finance_Products!M5</f>
+        <v>40000</v>
+      </c>
+      <c r="N5" t="str">
+        <f>Finance_Products!O5</f>
+        <v>ID, proof of address, income evidence, credit review and signed agreement</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="str">
+        <f>Finance_Products!A6</f>
+        <v>F005</v>
+      </c>
+      <c r="B6" t="str">
+        <f>IFERROR(INDEX(Finance_Partners!$B$2:$B$13,MATCH(Finance_Products!B6,Finance_Partners!$A$2:$A$13,0)),"")</f>
+        <v>HomeSolar Finance</v>
+      </c>
+      <c r="C6" t="str">
+        <f>Finance_Products!D6</f>
+        <v>Solar instalment plan</v>
+      </c>
+      <c r="D6" t="str">
+        <f>IF(AND(Finance_Request!$B$9&gt;=Finance_Products!G6,Finance_Request!$B$9&lt;=Finance_Products!H6),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="E6" t="str">
+        <f>IF(Finance_Request!$B$10&gt;=Finance_Products!I6,"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="F6" t="str">
+        <f>IF(AND(Finance_Request!$C$12&gt;=Finance_Products!J6,Finance_Request!$C$12&lt;=Finance_Products!K6),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="G6" t="str">
+        <f>IF(OR(Finance_Products!E6="All",Finance_Products!E6=Finance_Request!$B$13),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="H6" t="str">
+        <f>IF(OR(Finance_Products!F6="All",ISNUMBER(SEARCH(","&amp;LOWER(Finance_Request!$B$14)&amp;",",","&amp;LOWER(SUBSTITUTE(Finance_Products!F6,", ",","))&amp;","))),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="I6" t="str">
+        <f>IF(OR(Finance_Request!$B$11="Any",Finance_Request!$B$11=Finance_Products!D6),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J6" t="str">
+        <f>IF(AND(D6="YES",E6="YES",F6="YES",G6="YES",H6="YES",I6="YES",Finance_Request!$B$17="VALID"),"PRELIMINARY MATCH","NOT MATCHED")</f>
+        <v>NOT MATCHED</v>
+      </c>
+      <c r="K6" s="129" t="str">
+        <f>IF(AND(J6="PRELIMINARY MATCH",ISNUMBER([1]Finance_Products!L6),[1]Finance_Products!D6&lt;&gt;"Energy-as-a-Service / lease"),IF([1]Finance_Products!L6=0,[1]Customer_Scenario!$B$8/[1]Customer_Scenario!$B$11,-PMT([1]Finance_Products!L6/12,[1]Customer_Scenario!$B$11,[1]Customer_Scenario!$B$8))+[1]Finance_Products!N6,"")</f>
+        <v/>
+      </c>
+      <c r="L6" s="129" t="str">
+        <f>IF(ISNUMBER(K6),K6*[1]Customer_Scenario!$B$11+[1]Finance_Products!M6,"")</f>
+        <v/>
+      </c>
+      <c r="M6" s="129">
+        <f>[1]Finance_Products!M6</f>
+        <v>45000</v>
+      </c>
+      <c r="N6" t="str">
+        <f>Finance_Products!O6</f>
+        <v>ID, proof of address, income evidence, credit review and signed agreement</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="str">
+        <f>Finance_Products!A7</f>
+        <v>F006</v>
+      </c>
+      <c r="B7" t="str">
+        <f>IFERROR(INDEX(Finance_Partners!$B$2:$B$13,MATCH(Finance_Products!B7,Finance_Partners!$A$2:$A$13,0)),"")</f>
+        <v>SME Power Credit</v>
+      </c>
+      <c r="C7" t="str">
+        <f>Finance_Products!D7</f>
+        <v>Asset financing</v>
+      </c>
+      <c r="D7" t="str">
+        <f>IF(AND(Finance_Request!$B$9&gt;=Finance_Products!G7,Finance_Request!$B$9&lt;=Finance_Products!H7),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="E7" t="str">
+        <f>IF(Finance_Request!$B$10&gt;=Finance_Products!I7,"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="F7" t="str">
+        <f>IF(AND(Finance_Request!$C$12&gt;=Finance_Products!J7,Finance_Request!$C$12&lt;=Finance_Products!K7),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="G7" t="str">
+        <f>IF(OR(Finance_Products!E7="All",Finance_Products!E7=Finance_Request!$B$13),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="H7" t="str">
+        <f>IF(OR(Finance_Products!F7="All",ISNUMBER(SEARCH(","&amp;LOWER(Finance_Request!$B$14)&amp;",",","&amp;LOWER(SUBSTITUTE(Finance_Products!F7,", ",","))&amp;","))),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="I7" t="str">
+        <f>IF(OR(Finance_Request!$B$11="Any",Finance_Request!$B$11=Finance_Products!D7),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="J7" t="str">
+        <f>IF(AND(D7="YES",E7="YES",F7="YES",G7="YES",H7="YES",I7="YES",Finance_Request!$B$17="VALID"),"PRELIMINARY MATCH","NOT MATCHED")</f>
+        <v>PRELIMINARY MATCH</v>
+      </c>
+      <c r="K7" s="129">
+        <f>IF(AND(J7="PRELIMINARY MATCH",ISNUMBER([1]Finance_Products!L7),[1]Finance_Products!D7&lt;&gt;"Energy-as-a-Service / lease"),IF([1]Finance_Products!L7=0,[1]Customer_Scenario!$B$8/[1]Customer_Scenario!$B$11,-PMT([1]Finance_Products!L7/12,[1]Customer_Scenario!$B$11,[1]Customer_Scenario!$B$8))+[1]Finance_Products!N7,"")</f>
+        <v>248728.48128710786</v>
+      </c>
+      <c r="L7" s="129">
+        <f>IF(ISNUMBER(K7),K7*[1]Customer_Scenario!$B$11+[1]Finance_Products!M7,"")</f>
+        <v>9004225.3263358828</v>
+      </c>
+      <c r="M7" s="129">
+        <f>[1]Finance_Products!M7</f>
+        <v>50000</v>
+      </c>
+      <c r="N7" t="str">
+        <f>Finance_Products!O7</f>
+        <v>ID, proof of address, income evidence, credit review and signed agreement.</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="str">
+        <f>Finance_Products!A8</f>
+        <v>F007</v>
+      </c>
+      <c r="B8" t="str">
+        <f>IFERROR(INDEX(Finance_Partners!$B$2:$B$13,MATCH(Finance_Products!B8,Finance_Partners!$A$2:$A$13,0)),"")</f>
+        <v>Community Solar Plans</v>
+      </c>
+      <c r="C8" t="str">
+        <f>Finance_Products!D8</f>
+        <v>Solar instalment plan</v>
+      </c>
+      <c r="D8" t="str">
+        <f>IF(AND(Finance_Request!$B$9&gt;=Finance_Products!G8,Finance_Request!$B$9&lt;=Finance_Products!H8),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="E8" t="str">
+        <f>IF(Finance_Request!$B$10&gt;=Finance_Products!I8,"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="F8" t="str">
+        <f>IF(AND(Finance_Request!$C$12&gt;=Finance_Products!J8,Finance_Request!$C$12&lt;=Finance_Products!K8),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="G8" t="str">
+        <f>IF(OR(Finance_Products!E8="All",Finance_Products!E8=Finance_Request!$B$13),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="H8" t="str">
+        <f>IF(OR(Finance_Products!F8="All",ISNUMBER(SEARCH(","&amp;LOWER(Finance_Request!$B$14)&amp;",",","&amp;LOWER(SUBSTITUTE(Finance_Products!F8,", ",","))&amp;","))),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="I8" t="str">
+        <f>IF(OR(Finance_Request!$B$11="Any",Finance_Request!$B$11=Finance_Products!D8),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J8" t="str">
+        <f>IF(AND(D8="YES",E8="YES",F8="YES",G8="YES",H8="YES",I8="YES",Finance_Request!$B$17="VALID"),"PRELIMINARY MATCH","NOT MATCHED")</f>
+        <v>NOT MATCHED</v>
+      </c>
+      <c r="K8" s="129" t="str">
+        <f>IF(AND(J8="PRELIMINARY MATCH",ISNUMBER([1]Finance_Products!L8),[1]Finance_Products!D8&lt;&gt;"Energy-as-a-Service / lease"),IF([1]Finance_Products!L8=0,[1]Customer_Scenario!$B$8/[1]Customer_Scenario!$B$11,-PMT([1]Finance_Products!L8/12,[1]Customer_Scenario!$B$11,[1]Customer_Scenario!$B$8))+[1]Finance_Products!N8,"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="129" t="str">
+        <f>IF(ISNUMBER(K8),K8*[1]Customer_Scenario!$B$11+[1]Finance_Products!M8,"")</f>
+        <v/>
+      </c>
+      <c r="M8" s="129">
+        <f>[1]Finance_Products!M8</f>
+        <v>55000</v>
+      </c>
+      <c r="N8" t="str">
+        <f>Finance_Products!O8</f>
+        <v>ID, proof of address, income evidence, credit review and signed agreement</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="str">
+        <f>Finance_Products!A9</f>
+        <v>F008</v>
+      </c>
+      <c r="B9" t="str">
+        <f>IFERROR(INDEX(Finance_Partners!$B$2:$B$13,MATCH(Finance_Products!B9,Finance_Partners!$A$2:$A$13,0)),"")</f>
+        <v>Horizon Energy Services</v>
+      </c>
+      <c r="C9" t="str">
+        <f>Finance_Products!D9</f>
+        <v>Energy-as-a-Service / lease</v>
+      </c>
+      <c r="D9" t="str">
+        <f>IF(AND(Finance_Request!$B$9&gt;=Finance_Products!G9,Finance_Request!$B$9&lt;=Finance_Products!H9),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="E9" t="str">
+        <f>IF(Finance_Request!$B$10&gt;=Finance_Products!I9,"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="F9" t="str">
+        <f>IF(AND(Finance_Request!$C$12&gt;=Finance_Products!J9,Finance_Request!$C$12&lt;=Finance_Products!K9),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="G9" t="str">
+        <f>IF(OR(Finance_Products!E9="All",Finance_Products!E9=Finance_Request!$B$13),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="H9" t="str">
+        <f>IF(OR(Finance_Products!F9="All",ISNUMBER(SEARCH(","&amp;LOWER(Finance_Request!$B$14)&amp;",",","&amp;LOWER(SUBSTITUTE(Finance_Products!F9,", ",","))&amp;","))),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="I9" t="str">
+        <f>IF(OR(Finance_Request!$B$11="Any",Finance_Request!$B$11=Finance_Products!D9),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J9" t="str">
+        <f>IF(AND(D9="YES",E9="YES",F9="YES",G9="YES",H9="YES",I9="YES",Finance_Request!$B$17="VALID"),"PRELIMINARY MATCH","NOT MATCHED")</f>
+        <v>NOT MATCHED</v>
+      </c>
+      <c r="K9" s="129" t="str">
+        <f>IF(AND(J9="PRELIMINARY MATCH",ISNUMBER([1]Finance_Products!L9),[1]Finance_Products!D9&lt;&gt;"Energy-as-a-Service / lease"),IF([1]Finance_Products!L9=0,[1]Customer_Scenario!$B$8/[1]Customer_Scenario!$B$11,-PMT([1]Finance_Products!L9/12,[1]Customer_Scenario!$B$11,[1]Customer_Scenario!$B$8))+[1]Finance_Products!N9,"")</f>
+        <v/>
+      </c>
+      <c r="L9" s="129" t="str">
+        <f>IF(ISNUMBER(K9),K9*[1]Customer_Scenario!$B$11+[1]Finance_Products!M9,"")</f>
+        <v/>
+      </c>
+      <c r="M9" s="129">
+        <f>[1]Finance_Products!M9</f>
+        <v>60000</v>
+      </c>
+      <c r="N9" t="str">
+        <f>Finance_Products!O9</f>
+        <v>ID, address, income evidence; lender credit assessment. EaaS requires a separate usage-based quote</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="str">
+        <f>Finance_Products!A10</f>
+        <v>F009</v>
+      </c>
+      <c r="B10" t="str">
+        <f>IFERROR(INDEX(Finance_Partners!$B$2:$B$13,MATCH(Finance_Products!B10,Finance_Partners!$A$2:$A$13,0)),"")</f>
+        <v>SolarFlex Capital</v>
+      </c>
+      <c r="C10" t="str">
+        <f>Finance_Products!D10</f>
+        <v>Asset financing</v>
+      </c>
+      <c r="D10" t="str">
+        <f>IF(AND(Finance_Request!$B$9&gt;=Finance_Products!G10,Finance_Request!$B$9&lt;=Finance_Products!H10),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="E10" t="str">
+        <f>IF(Finance_Request!$B$10&gt;=Finance_Products!I10,"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="F10" t="str">
+        <f>IF(AND(Finance_Request!$C$12&gt;=Finance_Products!J10,Finance_Request!$C$12&lt;=Finance_Products!K10),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="G10" t="str">
+        <f>IF(OR(Finance_Products!E10="All",Finance_Products!E10=Finance_Request!$B$13),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="H10" t="str">
+        <f>IF(OR(Finance_Products!F10="All",ISNUMBER(SEARCH(","&amp;LOWER(Finance_Request!$B$14)&amp;",",","&amp;LOWER(SUBSTITUTE(Finance_Products!F10,", ",","))&amp;","))),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="I10" t="str">
+        <f>IF(OR(Finance_Request!$B$11="Any",Finance_Request!$B$11=Finance_Products!D10),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="J10" t="str">
+        <f>IF(AND(D10="YES",E10="YES",F10="YES",G10="YES",H10="YES",I10="YES",Finance_Request!$B$17="VALID"),"PRELIMINARY MATCH","NOT MATCHED")</f>
+        <v>PRELIMINARY MATCH</v>
+      </c>
+      <c r="K10" s="129">
+        <f>IF(AND(J10="PRELIMINARY MATCH",ISNUMBER([1]Finance_Products!L10),[1]Finance_Products!D10&lt;&gt;"Energy-as-a-Service / lease"),IF([1]Finance_Products!L10=0,[1]Customer_Scenario!$B$8/[1]Customer_Scenario!$B$11,-PMT([1]Finance_Products!L10/12,[1]Customer_Scenario!$B$11,[1]Customer_Scenario!$B$8))+[1]Finance_Products!N10,"")</f>
+        <v>270422.02587285126</v>
+      </c>
+      <c r="L10" s="129">
+        <f>IF(ISNUMBER(K10),K10*[1]Customer_Scenario!$B$11+[1]Finance_Products!M10,"")</f>
+        <v>9800192.9314226452</v>
+      </c>
+      <c r="M10" s="129">
+        <f>[1]Finance_Products!M10</f>
+        <v>65000</v>
+      </c>
+      <c r="N10" t="str">
+        <f>Finance_Products!O10</f>
+        <v>ID, proof of address, income evidence, credit review and signed agreement</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="str">
+        <f>Finance_Products!A11</f>
+        <v>F010</v>
+      </c>
+      <c r="B11" t="str">
+        <f>IFERROR(INDEX(Finance_Partners!$B$2:$B$13,MATCH(Finance_Products!B11,Finance_Partners!$A$2:$A$13,0)),"")</f>
+        <v>PowerPath Funding</v>
+      </c>
+      <c r="C11" t="str">
+        <f>Finance_Products!D11</f>
+        <v>Asset financing</v>
+      </c>
+      <c r="D11" t="str">
+        <f>IF(AND(Finance_Request!$B$9&gt;=Finance_Products!G11,Finance_Request!$B$9&lt;=Finance_Products!H11),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="E11" t="str">
+        <f>IF(Finance_Request!$B$10&gt;=Finance_Products!I11,"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="F11" t="str">
+        <f>IF(AND(Finance_Request!$C$12&gt;=Finance_Products!J11,Finance_Request!$C$12&lt;=Finance_Products!K11),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="G11" t="str">
+        <f>IF(OR(Finance_Products!E11="All",Finance_Products!E11=Finance_Request!$B$13),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="H11" t="str">
+        <f>IF(OR(Finance_Products!F11="All",ISNUMBER(SEARCH(","&amp;LOWER(Finance_Request!$B$14)&amp;",",","&amp;LOWER(SUBSTITUTE(Finance_Products!F11,", ",","))&amp;","))),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="I11" t="str">
+        <f>IF(OR(Finance_Request!$B$11="Any",Finance_Request!$B$11=Finance_Products!D11),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="J11" t="str">
+        <f>IF(AND(D11="YES",E11="YES",F11="YES",G11="YES",H11="YES",I11="YES",Finance_Request!$B$17="VALID"),"PRELIMINARY MATCH","NOT MATCHED")</f>
+        <v>PRELIMINARY MATCH</v>
+      </c>
+      <c r="K11" s="129">
+        <f>IF(AND(J11="PRELIMINARY MATCH",ISNUMBER([1]Finance_Products!L11),[1]Finance_Products!D11&lt;&gt;"Energy-as-a-Service / lease"),IF([1]Finance_Products!L11=0,[1]Customer_Scenario!$B$8/[1]Customer_Scenario!$B$11,-PMT([1]Finance_Products!L11/12,[1]Customer_Scenario!$B$11,[1]Customer_Scenario!$B$8))+[1]Finance_Products!N11,"")</f>
+        <v>277199.46935941442</v>
+      </c>
+      <c r="L11" s="129">
+        <f>IF(ISNUMBER(K11),K11*[1]Customer_Scenario!$B$11+[1]Finance_Products!M11,"")</f>
+        <v>10049180.89693892</v>
+      </c>
+      <c r="M11" s="129">
+        <f>[1]Finance_Products!M11</f>
+        <v>70000</v>
+      </c>
+      <c r="N11" t="str">
+        <f>Finance_Products!O11</f>
+        <v>ID, proof of address, income evidence, credit review and signed agreement</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="str">
+        <f>Finance_Products!A12</f>
+        <v>F011</v>
+      </c>
+      <c r="B12" t="str">
+        <f>IFERROR(INDEX(Finance_Partners!$B$2:$B$13,MATCH(Finance_Products!B12,Finance_Partners!$A$2:$A$13,0)),"")</f>
+        <v>SunNest Instalments</v>
+      </c>
+      <c r="C12" t="str">
+        <f>Finance_Products!D12</f>
+        <v>Solar instalment plan</v>
+      </c>
+      <c r="D12" t="str">
+        <f>IF(AND(Finance_Request!$B$9&gt;=Finance_Products!G12,Finance_Request!$B$9&lt;=Finance_Products!H12),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="E12" t="str">
+        <f>IF(Finance_Request!$B$10&gt;=Finance_Products!I12,"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="F12" t="str">
+        <f>IF(AND(Finance_Request!$C$12&gt;=Finance_Products!J12,Finance_Request!$C$12&lt;=Finance_Products!K12),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="G12" t="str">
+        <f>IF(OR(Finance_Products!E12="All",Finance_Products!E12=Finance_Request!$B$13),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="H12" t="str">
+        <f>IF(OR(Finance_Products!F12="All",ISNUMBER(SEARCH(","&amp;LOWER(Finance_Request!$B$14)&amp;",",","&amp;LOWER(SUBSTITUTE(Finance_Products!F12,", ",","))&amp;","))),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="I12" t="str">
+        <f>IF(OR(Finance_Request!$B$11="Any",Finance_Request!$B$11=Finance_Products!D12),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J12" t="str">
+        <f>IF(AND(D12="YES",E12="YES",F12="YES",G12="YES",H12="YES",I12="YES",Finance_Request!$B$17="VALID"),"PRELIMINARY MATCH","NOT MATCHED")</f>
+        <v>NOT MATCHED</v>
+      </c>
+      <c r="K12" s="129" t="str">
+        <f>IF(AND(J12="PRELIMINARY MATCH",ISNUMBER([1]Finance_Products!L12),[1]Finance_Products!D12&lt;&gt;"Energy-as-a-Service / lease"),IF([1]Finance_Products!L12=0,[1]Customer_Scenario!$B$8/[1]Customer_Scenario!$B$11,-PMT([1]Finance_Products!L12/12,[1]Customer_Scenario!$B$11,[1]Customer_Scenario!$B$8))+[1]Finance_Products!N12,"")</f>
+        <v/>
+      </c>
+      <c r="L12" s="129" t="str">
+        <f>IF(ISNUMBER(K12),K12*[1]Customer_Scenario!$B$11+[1]Finance_Products!M12,"")</f>
+        <v/>
+      </c>
+      <c r="M12" s="129">
+        <f>[1]Finance_Products!M12</f>
+        <v>75000</v>
+      </c>
+      <c r="N12" t="str">
+        <f>Finance_Products!O12</f>
+        <v>ID, proof of address, income evidence, credit review and signed agreement</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="str">
+        <f>Finance_Products!A13</f>
+        <v>F012</v>
+      </c>
+      <c r="B13" t="str">
+        <f>IFERROR(INDEX(Finance_Partners!$B$2:$B$13,MATCH(Finance_Products!B13,Finance_Partners!$A$2:$A$13,0)),"")</f>
+        <v>Commercial Energy Lease</v>
+      </c>
+      <c r="C13" t="str">
+        <f>Finance_Products!D13</f>
+        <v>Energy-as-a-Service / lease</v>
+      </c>
+      <c r="D13" t="str">
+        <f>IF(AND(Finance_Request!$B$9&gt;=Finance_Products!G13,Finance_Request!$B$9&lt;=Finance_Products!H13),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="E13" t="str">
+        <f>IF(Finance_Request!$B$10&gt;=Finance_Products!I13,"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="F13" t="str">
+        <f>IF(AND(Finance_Request!$C$12&gt;=Finance_Products!J13,Finance_Request!$C$12&lt;=Finance_Products!K13),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="G13" t="str">
+        <f>IF(OR(Finance_Products!E13="All",Finance_Products!E13=Finance_Request!$B$13),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="H13" t="str">
+        <f>IF(OR(Finance_Products!F13="All",ISNUMBER(SEARCH(","&amp;LOWER(Finance_Request!$B$14)&amp;",",","&amp;LOWER(SUBSTITUTE(Finance_Products!F13,", ",","))&amp;","))),"YES","NO")</f>
+        <v>YES</v>
+      </c>
+      <c r="I13" t="str">
+        <f>IF(OR(Finance_Request!$B$11="Any",Finance_Request!$B$11=Finance_Products!D13),"YES","NO")</f>
+        <v>NO</v>
+      </c>
+      <c r="J13" t="str">
+        <f>IF(AND(D13="YES",E13="YES",F13="YES",G13="YES",H13="YES",I13="YES",Finance_Request!$B$17="VALID"),"PRELIMINARY MATCH","NOT MATCHED")</f>
+        <v>NOT MATCHED</v>
+      </c>
+      <c r="K13" s="129" t="str">
+        <f>IF(AND(J13="PRELIMINARY MATCH",ISNUMBER([1]Finance_Products!L13),[1]Finance_Products!D13&lt;&gt;"Energy-as-a-Service / lease"),IF([1]Finance_Products!L13=0,[1]Customer_Scenario!$B$8/[1]Customer_Scenario!$B$11,-PMT([1]Finance_Products!L13/12,[1]Customer_Scenario!$B$11,[1]Customer_Scenario!$B$8))+[1]Finance_Products!N13,"")</f>
+        <v/>
+      </c>
+      <c r="L13" s="129" t="str">
+        <f>IF(ISNUMBER(K13),K13*[1]Customer_Scenario!$B$11+[1]Finance_Products!M13,"")</f>
+        <v/>
+      </c>
+      <c r="M13" s="129">
+        <f>[1]Finance_Products!M13</f>
+        <v>80000</v>
+      </c>
+      <c r="N13" t="str">
+        <f>Finance_Products!O13</f>
+        <v>ID, address, income evidence, lender credit assessment, EaaS requires a separate usage-based quote</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14EB6DC3-2555-434F-B72A-B6C6BACA1FDA}">
+  <sheetPr>
+    <tabColor rgb="FF0070C0"/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="35.36328125" customWidth="1"/>
+    <col min="2" max="2" width="69.54296875" customWidth="1"/>
+    <col min="3" max="3" width="65.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="21.5" customHeight="1">
+      <c r="A1" s="128" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B1" s="128" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C1" s="128"/>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B2" s="126" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B3" t="str">
+        <f>IFERROR(INDEX(Finance_Matches!$B$2:$B$13,MATCH(B2,Finance_Matches!$A$2:$A$13,0)),"")</f>
+        <v>SunBridge Capital</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B4" t="str">
+        <f>IFERROR(INDEX(Finance_Products!$C$2:$C$13,MATCH($B$2,Finance_Products!$A$2:$A$13,0)),"")</f>
+        <v>SunBridge Asset Loan</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B5" t="str">
+        <f>IFERROR(INDEX(Finance_Products!$D$2:$D$13,MATCH($B$2,Finance_Products!$A$2:$A$13,0)),"")</f>
+        <v>Asset financing</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B6" t="str">
+        <f>IFERROR(INDEX(Finance_Matches!$J$2:$J$13,MATCH(B2,Finance_Matches!$A$2:$A$13,0)),"NOT FOUND")</f>
+        <v>PRELIMINARY MATCH</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B7" s="124">
+        <f>Finance_Request!B9</f>
+        <v>4500000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B8" s="124">
+        <f>Finance_Request!B8</f>
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B9" t="str">
+        <f>Finance_Request!B12</f>
+        <v>24-36 months</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B10" s="125">
+        <f>IFERROR(INDEX(Finance_Products!$L$2:$L$13,MATCH($B$2,Finance_Products!$A$2:$A$13,0)),"")</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B11" s="129" t="str">
+        <f>IFERROR(INDEX([1]Finance_Matches!$K$2:$K$13,MATCH(B2,[1]Finance_Matches!$A$2:$A$13,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B12" s="129">
+        <f>IFERROR(INDEX(Finance_Products!$M$2:$M$13,MATCH($B$2,Finance_Products!$A$2:$A$13,0)),"")</f>
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B13" s="129">
+        <f>IFERROR(INDEX(Finance_Matches!$L$2:$L$13,MATCH(B2,Finance_Matches!$A$2:$A$13,0)),"")</f>
+        <v>9247676.3265405148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B14" t="str">
+        <f>IFERROR(INDEX([1]Finance_Products!$O$2:$O$13,MATCH($B$2,[1]Finance_Products!$A$2:$A$13,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B16" t="str">
+        <f>Finance_Request!B16</f>
+        <v>Yes</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -21378,16 +24443,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="24" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="130" t="s">
         <v>313</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="28" t="s">
@@ -38342,18 +41407,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="130" t="s">
         <v>498</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="13" t="s">
@@ -38393,11 +41458,11 @@
     <row r="4" spans="1:12">
       <c r="A4" s="46" t="str">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+0)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+0)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$D$1:$D$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+0),""),"")</f>
-        <v>Room Lights</v>
+        <v>LED Bulbs</v>
       </c>
       <c r="B4" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+0)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+0)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$E$1:$E$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+0),""),"")</f>
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="C4" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+0)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+0)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$F$1:$F$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+0),""),"")</f>
@@ -38405,7 +41470,7 @@
       </c>
       <c r="D4" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+0)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+0)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$G$1:$G$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+0),""),"")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+0)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+0)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$H$1:$H$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+0),""),"")</f>
@@ -38417,40 +41482,40 @@
       </c>
       <c r="G4" s="65">
         <f t="shared" ref="G4:G23" si="1">IFERROR(F4*B4*D4/1000,0)</f>
-        <v>7</v>
+        <v>1.2</v>
       </c>
       <c r="H4" s="14">
         <f t="shared" ref="H4:H23" si="2">G4*30</f>
-        <v>210</v>
+        <v>36</v>
       </c>
       <c r="I4" s="18">
         <f t="shared" ref="I4:I22" si="3">IFERROR(F4*B4,0)</f>
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="K4" t="s">
         <v>322</v>
       </c>
       <c r="L4" s="17">
         <f>SUM(G4:G23)</f>
-        <v>96.45</v>
+        <v>13.397500000000003</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="46" t="str">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+1)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+1)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$D$1:$D$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+1),""),"")</f>
-        <v>Common Area Lights</v>
+        <v>Fans</v>
       </c>
       <c r="B5" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+1)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+1)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$E$1:$E$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+1),""),"")</f>
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="C5" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+1)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+1)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$F$1:$F$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+1),""),"")</f>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="D5" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+1)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+1)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$G$1:$G$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+1),""),"")</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E5" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+1)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+1)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$H$1:$H$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+1),""),"")</f>
@@ -38458,40 +41523,40 @@
       </c>
       <c r="F5" s="14">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="G5" s="65">
         <f t="shared" si="1"/>
-        <v>9.6</v>
+        <v>2.88</v>
       </c>
       <c r="H5" s="14">
         <f t="shared" si="2"/>
-        <v>288</v>
+        <v>86.399999999999991</v>
       </c>
       <c r="I5" s="18">
         <f t="shared" si="3"/>
-        <v>800</v>
+        <v>360</v>
       </c>
       <c r="K5" t="s">
         <v>504</v>
       </c>
       <c r="L5" s="14">
         <f>SUM(H4:H23)</f>
-        <v>2893.5</v>
+        <v>401.92499999999995</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="46" t="str">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+2)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+2)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$D$1:$D$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+2),""),"")</f>
-        <v>Selected Room AC</v>
+        <v>Television</v>
       </c>
       <c r="B6" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+2)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+2)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$E$1:$E$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+2),""),"")</f>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C6" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+2)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+2)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$F$1:$F$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+2),""),"")</f>
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="D6" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+2)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+2)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$G$1:$G$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+2),""),"")</f>
@@ -38499,48 +41564,48 @@
       </c>
       <c r="E6" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+2)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+2)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$H$1:$H$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+2),""),"")</f>
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="F6" s="14">
         <f t="shared" si="0"/>
-        <v>540</v>
+        <v>100</v>
       </c>
       <c r="G6" s="65">
         <f t="shared" si="1"/>
-        <v>32.4</v>
+        <v>1.2</v>
       </c>
       <c r="H6" s="14">
         <f t="shared" si="2"/>
-        <v>972</v>
+        <v>36</v>
       </c>
       <c r="I6" s="18">
         <f t="shared" si="3"/>
-        <v>5400</v>
+        <v>200</v>
       </c>
       <c r="K6" t="s">
         <v>505</v>
       </c>
       <c r="L6" s="14">
         <f>SUM(I4:I23)/1000</f>
-        <v>16.8</v>
+        <v>3.7725</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="46" t="str">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+3)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+3)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$D$1:$D$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+3),""),"")</f>
-        <v>Reception/Office</v>
+        <v>Decoder</v>
       </c>
       <c r="B7" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+3)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+3)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$E$1:$E$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+3),""),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+3)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+3)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$F$1:$F$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+3),""),"")</f>
-        <v>600</v>
+        <v>25</v>
       </c>
       <c r="D7" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+3)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+3)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$G$1:$G$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+3),""),"")</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E7" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+3)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+3)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$H$1:$H$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+3),""),"")</f>
@@ -38548,32 +41613,32 @@
       </c>
       <c r="F7" s="14">
         <f t="shared" si="0"/>
-        <v>600</v>
+        <v>25</v>
       </c>
       <c r="G7" s="65">
         <f t="shared" si="1"/>
-        <v>7.2</v>
+        <v>0.3</v>
       </c>
       <c r="H7" s="14">
         <f t="shared" si="2"/>
-        <v>216</v>
+        <v>9</v>
       </c>
       <c r="I7" s="18">
         <f t="shared" si="3"/>
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="K7" t="s">
         <v>506</v>
       </c>
       <c r="L7" s="14">
         <f>L6*0.65</f>
-        <v>10.920000000000002</v>
+        <v>2.4521250000000001</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="46" t="str">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+4)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+4)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$D$1:$D$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+4),""),"")</f>
-        <v>WiFi/CCTV/Access Control</v>
+        <v>Refrigerator</v>
       </c>
       <c r="B8" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+4)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+4)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$E$1:$E$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+4),""),"")</f>
@@ -38581,7 +41646,7 @@
       </c>
       <c r="C8" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+4)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+4)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$F$1:$F$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+4),""),"")</f>
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="D8" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+4)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+4)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$G$1:$G$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+4),""),"")</f>
@@ -38589,41 +41654,41 @@
       </c>
       <c r="E8" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+4)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+4)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$H$1:$H$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+4),""),"")</f>
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F8" s="14">
         <f t="shared" si="0"/>
-        <v>400</v>
+        <v>60</v>
       </c>
       <c r="G8" s="65">
         <f t="shared" si="1"/>
-        <v>9.6</v>
+        <v>1.44</v>
       </c>
       <c r="H8" s="14">
         <f t="shared" si="2"/>
-        <v>288</v>
+        <v>43.199999999999996</v>
       </c>
       <c r="I8" s="18">
         <f t="shared" si="3"/>
-        <v>400</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="46" t="str">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+5)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+5)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$D$1:$D$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+5),""),"")</f>
-        <v>Water Pump</v>
+        <v>WiFi Router</v>
       </c>
       <c r="B9" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+5)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+5)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$E$1:$E$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+5),""),"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+5)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+5)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$F$1:$F$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+5),""),"")</f>
-        <v>1500</v>
+        <v>15</v>
       </c>
       <c r="D9" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+5)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+5)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$G$1:$G$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+5),""),"")</f>
-        <v>2.5</v>
+        <v>24</v>
       </c>
       <c r="E9" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+5)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+5)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$H$1:$H$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+5),""),"")</f>
@@ -38631,19 +41696,19 @@
       </c>
       <c r="F9" s="14">
         <f t="shared" si="0"/>
-        <v>1500</v>
+        <v>15</v>
       </c>
       <c r="G9" s="65">
         <f t="shared" si="1"/>
-        <v>7.5</v>
+        <v>0.36</v>
       </c>
       <c r="H9" s="14">
         <f t="shared" si="2"/>
-        <v>225</v>
+        <v>10.799999999999999</v>
       </c>
       <c r="I9" s="18">
         <f t="shared" si="3"/>
-        <v>3000</v>
+        <v>15</v>
       </c>
       <c r="K9" t="s">
         <v>938</v>
@@ -38656,57 +41721,57 @@
     <row r="10" spans="1:12">
       <c r="A10" s="46" t="str">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+6)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+6)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$D$1:$D$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+6),""),"")</f>
-        <v>Kitchen Refrigeration</v>
+        <v>Laptop</v>
       </c>
       <c r="B10" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+6)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+6)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$E$1:$E$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+6),""),"")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+6)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+6)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$F$1:$F$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+6),""),"")</f>
-        <v>300</v>
+        <v>65</v>
       </c>
       <c r="D10" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+6)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+6)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$G$1:$G$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+6),""),"")</f>
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E10" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+6)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+6)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$H$1:$H$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+6),""),"")</f>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F10" s="14">
         <f t="shared" si="0"/>
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="G10" s="65">
         <f t="shared" si="1"/>
-        <v>14.4</v>
+        <v>0.97499999999999998</v>
       </c>
       <c r="H10" s="14">
         <f t="shared" si="2"/>
-        <v>432</v>
+        <v>29.25</v>
       </c>
       <c r="I10" s="18">
         <f t="shared" si="3"/>
-        <v>600</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="46" t="str">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+7)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+7)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$D$1:$D$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+7),""),"")</f>
-        <v>Kitchen Equipment Allowance</v>
+        <v>Phone Chargers</v>
       </c>
       <c r="B11" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+7)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+7)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$E$1:$E$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+7),""),"")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C11" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+7)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+7)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$F$1:$F$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+7),""),"")</f>
-        <v>2500</v>
+        <v>10</v>
       </c>
       <c r="D11" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+7)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+7)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$G$1:$G$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+7),""),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+7)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+7)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$H$1:$H$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+7),""),"")</f>
@@ -38714,25 +41779,25 @@
       </c>
       <c r="F11" s="14">
         <f t="shared" si="0"/>
-        <v>2500</v>
+        <v>10</v>
       </c>
       <c r="G11" s="65">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>0.15</v>
       </c>
       <c r="H11" s="14">
         <f t="shared" si="2"/>
-        <v>150</v>
+        <v>4.5</v>
       </c>
       <c r="I11" s="18">
         <f t="shared" si="3"/>
-        <v>2500</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="46" t="str">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+8)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+8)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$D$1:$D$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+8),""),"")</f>
-        <v>Laundry Equipment Allowance</v>
+        <v>Deep Freezer</v>
       </c>
       <c r="B12" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+8)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+8)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$E$1:$E$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+8),""),"")</f>
@@ -38740,183 +41805,183 @@
       </c>
       <c r="C12" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+8)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+8)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$F$1:$F$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+8),""),"")</f>
-        <v>2500</v>
+        <v>250</v>
       </c>
       <c r="D12" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+8)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+8)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$G$1:$G$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+8),""),"")</f>
-        <v>1.5</v>
+        <v>24</v>
       </c>
       <c r="E12" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+8)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+8)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$H$1:$H$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+8),""),"")</f>
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="F12" s="14">
         <f t="shared" si="0"/>
-        <v>2500</v>
+        <v>112.5</v>
       </c>
       <c r="G12" s="65">
         <f t="shared" si="1"/>
-        <v>3.75</v>
+        <v>2.7</v>
       </c>
       <c r="H12" s="14">
         <f t="shared" si="2"/>
-        <v>112.5</v>
+        <v>81</v>
       </c>
       <c r="I12" s="18">
         <f t="shared" si="3"/>
-        <v>2500</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="46" t="str">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+9)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+9)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$D$1:$D$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+9),""),"")</f>
-        <v/>
-      </c>
-      <c r="B13" s="55" t="str">
+        <v>Microwave</v>
+      </c>
+      <c r="B13" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+9)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+9)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$E$1:$E$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+9),""),"")</f>
-        <v/>
-      </c>
-      <c r="C13" s="55" t="str">
+        <v>1</v>
+      </c>
+      <c r="C13" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+9)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+9)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$F$1:$F$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+9),""),"")</f>
-        <v/>
-      </c>
-      <c r="D13" s="55" t="str">
+        <v>1200</v>
+      </c>
+      <c r="D13" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+9)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+9)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$G$1:$G$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+9),""),"")</f>
-        <v/>
-      </c>
-      <c r="E13" s="55" t="str">
+        <v>0.4</v>
+      </c>
+      <c r="E13" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+9)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+9)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$H$1:$H$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+9),""),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F13" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G13" s="65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="H13" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>14.399999999999999</v>
       </c>
       <c r="I13" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="46" t="str">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+10)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+10)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$D$1:$D$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+10),""),"")</f>
-        <v/>
-      </c>
-      <c r="B14" s="55" t="str">
+        <v>Washing Machine</v>
+      </c>
+      <c r="B14" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+10)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+10)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$E$1:$E$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+10),""),"")</f>
-        <v/>
-      </c>
-      <c r="C14" s="55" t="str">
+        <v>1</v>
+      </c>
+      <c r="C14" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+10)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+10)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$F$1:$F$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+10),""),"")</f>
-        <v/>
-      </c>
-      <c r="D14" s="55" t="str">
+        <v>500</v>
+      </c>
+      <c r="D14" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+10)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+10)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$G$1:$G$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+10),""),"")</f>
-        <v/>
-      </c>
-      <c r="E14" s="55" t="str">
+        <v>0.7</v>
+      </c>
+      <c r="E14" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+10)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+10)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$H$1:$H$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+10),""),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F14" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G14" s="65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="H14" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="I14" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="46" t="str">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+11)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+11)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$D$1:$D$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+11),""),"")</f>
-        <v/>
-      </c>
-      <c r="B15" s="55" t="str">
+        <v>Water Pump</v>
+      </c>
+      <c r="B15" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+11)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+11)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$E$1:$E$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+11),""),"")</f>
-        <v/>
-      </c>
-      <c r="C15" s="55" t="str">
+        <v>1</v>
+      </c>
+      <c r="C15" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+11)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+11)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$F$1:$F$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+11),""),"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="55" t="str">
+        <v>750</v>
+      </c>
+      <c r="D15" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+11)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+11)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$G$1:$G$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+11),""),"")</f>
-        <v/>
-      </c>
-      <c r="E15" s="55" t="str">
+        <v>0.75</v>
+      </c>
+      <c r="E15" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+11)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+11)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$H$1:$H$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+11),""),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F15" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>750</v>
       </c>
       <c r="G15" s="65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.5625</v>
       </c>
       <c r="H15" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>16.875</v>
       </c>
       <c r="I15" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>750</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="46" t="str">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+12)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+12)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$D$1:$D$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+12),""),"")</f>
-        <v/>
-      </c>
-      <c r="B16" s="55" t="str">
+        <v>Security Lights</v>
+      </c>
+      <c r="B16" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+12)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+12)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$E$1:$E$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+12),""),"")</f>
-        <v/>
-      </c>
-      <c r="C16" s="55" t="str">
+        <v>4</v>
+      </c>
+      <c r="C16" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+12)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+12)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$F$1:$F$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+12),""),"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="55" t="str">
+        <v>20</v>
+      </c>
+      <c r="D16" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+12)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+12)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$G$1:$G$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+12),""),"")</f>
-        <v/>
-      </c>
-      <c r="E16" s="55" t="str">
+        <v>10</v>
+      </c>
+      <c r="E16" s="55">
         <f>IFERROR(IF(AND(VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,3,FALSE)=User_Inputs!$B$10,INDEX(Appliance_Library!$A$1:$A$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+12)=User_Inputs!$B$10,INDEX(Appliance_Library!$B$1:$B$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+12)=VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,4,FALSE)),INDEX(Appliance_Library!$H$1:$H$312,VLOOKUP(User_Inputs!$D$11,Appliance_Library!$Q$4:$T$43,2,FALSE)+12),""),"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F16" s="14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G16" s="65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="H16" s="14">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I16" s="18">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -39321,18 +42386,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="24" customHeight="1">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="130" t="s">
         <v>507</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
-      <c r="I1" s="119"/>
-      <c r="J1" s="119"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
+      <c r="I1" s="131"/>
+      <c r="J1" s="131"/>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="13" t="s">
@@ -39985,14 +43050,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" customHeight="1">
-      <c r="A1" s="120"/>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="119"/>
-      <c r="H1" s="119"/>
+      <c r="A1" s="130"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
+      <c r="D1" s="131"/>
+      <c r="E1" s="131"/>
+      <c r="F1" s="131"/>
+      <c r="G1" s="131"/>
+      <c r="H1" s="131"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="13"/>
@@ -40077,13 +43142,13 @@
     <row r="12" spans="1:8">
       <c r="B12" s="105">
         <f>Diesel_Economics!B12</f>
-        <v>34722</v>
+        <v>3617.3249999999998</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="B13" s="105">
         <f>Diesel_Economics!B11</f>
-        <v>0</v>
+        <v>1205.7749999999999</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -40097,13 +43162,13 @@
     <row r="16" spans="1:8">
       <c r="B16" s="105">
         <f>Diesel_Economics!B12</f>
-        <v>34722</v>
+        <v>3617.3249999999998</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="105">
         <f>MAX(0,Diesel_Economics!B12-Diesel_Economics!B24)</f>
-        <v>3184.5</v>
+        <v>473.09999999999945</v>
       </c>
     </row>
     <row r="18" spans="2:2">
@@ -40115,13 +43180,13 @@
     <row r="20" spans="2:2">
       <c r="B20" s="105">
         <f>Solar_Sizing!B14</f>
-        <v>31537.5</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="105">
         <f>MAX(0,Diesel_Economics!B12-Diesel_Economics!B24)</f>
-        <v>3184.5</v>
+        <v>473.09999999999945</v>
       </c>
     </row>
     <row r="22" spans="2:2">
